--- a/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_variable_hrp_quarterly.xlsx
+++ b/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_variable_hrp_quarterly.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU10"/>
+  <dimension ref="A1:AU9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -956,12 +956,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -982,66 +982,70 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>39364</v>
+        <v>43880</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>40486</v>
-      </c>
+        <v>44846</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>775</v>
+        <v>1474</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.3674998761946072</v>
+        <v>-0.3830918012000365</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.3674998761946072</v>
+        <v>-0.3830918012000365</v>
       </c>
       <c r="P4" t="n">
-        <v>774</v>
+        <v>1474</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.1532547245176263</v>
+        <v>0.2241534346522962</v>
       </c>
       <c r="R4" t="b">
         <v>0</v>
       </c>
       <c r="S4" t="b">
-        <v>0</v>
-      </c>
-      <c r="T4" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="T4" s="3" t="n">
+        <v>-0.02196843025820727</v>
+      </c>
       <c r="U4" t="n">
-        <v>355</v>
+        <v>668</v>
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" s="3" t="n">
-        <v>-0.3674998761946072</v>
+        <v>-0.3830918012000365</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>-0.3674998761946072</v>
+        <v>-0.3830918012000365</v>
       </c>
       <c r="Y4" t="b">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>420</v>
+        <v>806</v>
       </c>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" s="3" t="n">
-        <v>0.5810273585142876</v>
+        <v>0.6209867237058013</v>
       </c>
       <c r="AD4" s="3" t="n">
         <v>0.8333333333333334</v>
@@ -1052,43 +1056,43 @@
         </is>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="AH4" s="3" t="n">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="AJ4" s="3" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>5/6</t>
+        </is>
+      </c>
+      <c r="AL4" s="3" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>5/6</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="AK4" t="inlineStr">
+      <c r="AO4" t="inlineStr">
         <is>
           <t>4/6</t>
-        </is>
-      </c>
-      <c r="AL4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>6/6</t>
-        </is>
-      </c>
-      <c r="AN4" s="3" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>2/6</t>
         </is>
       </c>
       <c r="AP4" s="3" t="inlineStr"/>
@@ -1106,7 +1110,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1137,60 +1141,60 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>43880</v>
+        <v>39364</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>44846</v>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
+        <v>39881</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>40486</v>
+      </c>
       <c r="M5" t="n">
-        <v>1474</v>
+        <v>775</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-0.3830918012000365</v>
+        <v>-0.367499876194607</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-0.3830918012000365</v>
+        <v>-0.367499876194607</v>
       </c>
       <c r="P5" t="n">
-        <v>1474</v>
+        <v>774</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.2241534346522962</v>
+        <v>0.1532547245176262</v>
       </c>
       <c r="R5" t="b">
         <v>0</v>
       </c>
       <c r="S5" t="b">
-        <v>1</v>
-      </c>
-      <c r="T5" s="3" t="n">
-        <v>-0.02196843025820727</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T5" s="3" t="inlineStr"/>
       <c r="U5" t="n">
-        <v>668</v>
+        <v>355</v>
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" s="3" t="n">
-        <v>-0.3830918012000365</v>
+        <v>-0.367499876194607</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>-0.3830918012000365</v>
+        <v>-0.367499876194607</v>
       </c>
       <c r="Y5" t="b">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>806</v>
+        <v>420</v>
       </c>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" s="3" t="n">
-        <v>0.6209867237058013</v>
+        <v>0.5810273585142871</v>
       </c>
       <c r="AD5" s="3" t="n">
         <v>0.8333333333333334</v>
@@ -1209,35 +1213,35 @@
         </is>
       </c>
       <c r="AH5" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="AJ5" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.5</v>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="AL5" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.5</v>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="AN5" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="AP5" s="3" t="inlineStr"/>
@@ -1255,7 +1259,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1273,49 +1277,45 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>39364</v>
+        <v>36865</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>39881</v>
+        <v>37460</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>40486</v>
+        <v>39209</v>
       </c>
       <c r="M6" t="n">
-        <v>775</v>
+        <v>1610</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.367499876194607</v>
+        <v>-0.4201681847926454</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.367499876194607</v>
+        <v>-0.4201681847926454</v>
       </c>
       <c r="P6" t="n">
-        <v>774</v>
+        <v>1609</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.1532547245176262</v>
+        <v>0.2257090305445466</v>
       </c>
       <c r="R6" t="b">
         <v>0</v>
@@ -1325,25 +1325,25 @@
       </c>
       <c r="T6" s="3" t="inlineStr"/>
       <c r="U6" t="n">
-        <v>355</v>
+        <v>405</v>
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" s="3" t="n">
-        <v>-0.367499876194607</v>
+        <v>-0.4201681847926454</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>-0.367499876194607</v>
+        <v>-0.4201681847926454</v>
       </c>
       <c r="Y6" t="b">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>420</v>
+        <v>1205</v>
       </c>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" s="3" t="n">
-        <v>0.5810273585142871</v>
+        <v>0.724638030844148</v>
       </c>
       <c r="AD6" s="3" t="n">
         <v>0.8333333333333334</v>
@@ -1393,30 +1393,12 @@
           <t>2/6</t>
         </is>
       </c>
-      <c r="AP6" s="3" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>1/6</t>
-        </is>
-      </c>
-      <c r="AR6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>0/6</t>
-        </is>
-      </c>
-      <c r="AT6" s="3" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>2/6</t>
-        </is>
-      </c>
+      <c r="AP6" s="3" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" s="3" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1426,7 +1408,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1457,32 +1439,32 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>36865</v>
+        <v>39364</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>37460</v>
+        <v>39881</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>39209</v>
+        <v>40567</v>
       </c>
       <c r="M7" t="n">
-        <v>1610</v>
+        <v>829</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>-0.4201681847926454</v>
+        <v>-0.4000942896051514</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>-0.4201681847926454</v>
+        <v>-0.4000942896051514</v>
       </c>
       <c r="P7" t="n">
-        <v>1609</v>
+        <v>828</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.2257090305445466</v>
+        <v>0.1700991045634238</v>
       </c>
       <c r="R7" t="b">
         <v>0</v>
@@ -1492,25 +1474,25 @@
       </c>
       <c r="T7" s="3" t="inlineStr"/>
       <c r="U7" t="n">
-        <v>405</v>
+        <v>355</v>
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" s="3" t="n">
-        <v>-0.4201681847926454</v>
+        <v>-0.4000942896051514</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>-0.4201681847926454</v>
+        <v>-0.4000942896051514</v>
       </c>
       <c r="Y7" t="b">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1205</v>
+        <v>474</v>
       </c>
       <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" s="3" t="n">
-        <v>0.724638030844148</v>
+        <v>0.6669286234028602</v>
       </c>
       <c r="AD7" s="3" t="n">
         <v>0.8333333333333334</v>
@@ -1537,11 +1519,11 @@
         </is>
       </c>
       <c r="AJ7" s="3" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="AL7" s="3" t="n">
@@ -1575,7 +1557,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1593,49 +1575,45 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>39364</v>
+        <v>43880</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>39881</v>
+        <v>43913</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>40567</v>
+        <v>45344</v>
       </c>
       <c r="M8" t="n">
-        <v>829</v>
+        <v>1009</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.4000942896051514</v>
+        <v>-0.2902464771828116</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.4000942896051514</v>
+        <v>-0.2902464771828116</v>
       </c>
       <c r="P8" t="n">
-        <v>828</v>
+        <v>1008</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.1700991045634238</v>
+        <v>0.1757123133222559</v>
       </c>
       <c r="R8" t="b">
         <v>0</v>
@@ -1645,25 +1623,25 @@
       </c>
       <c r="T8" s="3" t="inlineStr"/>
       <c r="U8" t="n">
-        <v>355</v>
+        <v>23</v>
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" s="3" t="n">
-        <v>-0.4000942896051514</v>
+        <v>-0.2902464771828116</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>-0.4000942896051514</v>
+        <v>-0.2902464771828116</v>
       </c>
       <c r="Y8" t="b">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>474</v>
+        <v>986</v>
       </c>
       <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" s="3" t="n">
-        <v>0.6669286234028602</v>
+        <v>0.4089398190385178</v>
       </c>
       <c r="AD8" s="3" t="n">
         <v>0.8333333333333334</v>
@@ -1682,61 +1660,43 @@
         </is>
       </c>
       <c r="AH8" s="3" t="n">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="AL8" s="3" t="n">
-        <v>0.5</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="AN8" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>2/6</t>
-        </is>
-      </c>
-      <c r="AP8" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>3/6</t>
-        </is>
-      </c>
-      <c r="AR8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>0/6</t>
-        </is>
-      </c>
-      <c r="AT8" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>3/6</t>
-        </is>
-      </c>
+          <t>4/6</t>
+        </is>
+      </c>
+      <c r="AP8" s="3" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" s="3" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1746,7 +1706,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1777,32 +1737,32 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>43880</v>
+        <v>39364</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>43913</v>
+        <v>39881</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>45344</v>
+        <v>40546</v>
       </c>
       <c r="M9" t="n">
-        <v>1009</v>
+        <v>815</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>-0.2902464771828116</v>
+        <v>-0.3816212997058296</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.2902464771828116</v>
+        <v>-0.3816212997058296</v>
       </c>
       <c r="P9" t="n">
-        <v>1008</v>
+        <v>814</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.1757123133222559</v>
+        <v>0.1642351393340293</v>
       </c>
       <c r="R9" t="b">
         <v>0</v>
@@ -1812,25 +1772,25 @@
       </c>
       <c r="T9" s="3" t="inlineStr"/>
       <c r="U9" t="n">
-        <v>23</v>
+        <v>355</v>
       </c>
       <c r="V9" t="inlineStr"/>
       <c r="W9" s="3" t="n">
-        <v>-0.2902464771828116</v>
+        <v>-0.3816212997058296</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>-0.2902464771828116</v>
+        <v>-0.3816212997058296</v>
       </c>
       <c r="Y9" t="b">
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>986</v>
+        <v>460</v>
       </c>
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" s="3" t="n">
-        <v>0.4089398190385178</v>
+        <v>0.6171320252852945</v>
       </c>
       <c r="AD9" s="3" t="n">
         <v>0.8333333333333334</v>
@@ -1849,35 +1809,35 @@
         </is>
       </c>
       <c r="AH9" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>3/6</t>
+        </is>
+      </c>
+      <c r="AJ9" s="3" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>2/6</t>
+        </is>
+      </c>
+      <c r="AL9" s="3" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="AI9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>4/6</t>
         </is>
       </c>
-      <c r="AJ9" s="3" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>4/6</t>
-        </is>
-      </c>
-      <c r="AL9" s="3" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>5/6</t>
-        </is>
-      </c>
       <c r="AN9" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="AP9" s="3" t="inlineStr"/>
@@ -1886,177 +1846,6 @@
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" s="3" t="inlineStr"/>
       <c r="AU9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>hrp</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>39364</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>40546</v>
-      </c>
-      <c r="M10" t="n">
-        <v>815</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.3816212997058296</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.3816212997058296</v>
-      </c>
-      <c r="P10" t="n">
-        <v>814</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.1642351393340293</v>
-      </c>
-      <c r="R10" t="b">
-        <v>0</v>
-      </c>
-      <c r="S10" t="b">
-        <v>0</v>
-      </c>
-      <c r="T10" s="3" t="inlineStr"/>
-      <c r="U10" t="n">
-        <v>355</v>
-      </c>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" s="3" t="n">
-        <v>-0.3816212997058296</v>
-      </c>
-      <c r="X10" s="3" t="n">
-        <v>-0.3816212997058296</v>
-      </c>
-      <c r="Y10" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>460</v>
-      </c>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" s="3" t="n">
-        <v>0.6171320252852945</v>
-      </c>
-      <c r="AD10" s="3" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>5/6</t>
-        </is>
-      </c>
-      <c r="AF10" s="3" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>5/6</t>
-        </is>
-      </c>
-      <c r="AH10" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>3/6</t>
-        </is>
-      </c>
-      <c r="AJ10" s="3" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>2/6</t>
-        </is>
-      </c>
-      <c r="AL10" s="3" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>4/6</t>
-        </is>
-      </c>
-      <c r="AN10" s="3" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>2/6</t>
-        </is>
-      </c>
-      <c r="AP10" s="3" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>2/6</t>
-        </is>
-      </c>
-      <c r="AR10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>0/6</t>
-        </is>
-      </c>
-      <c r="AT10" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>3/6</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2069,7 +1858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO10"/>
+  <dimension ref="A1:AO9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2543,12 +2332,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2558,7 +2347,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2569,41 +2358,45 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
         <v>36608</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>37460</v>
+        <v>36650</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>37776</v>
+        <v>36691</v>
       </c>
       <c r="M4" t="n">
-        <v>801</v>
+        <v>57</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.2100718359282402</v>
+        <v>-0.05180660636782208</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.3100613758801871</v>
+        <v>-0.07968906534569831</v>
       </c>
       <c r="P4" t="n">
-        <v>276</v>
+        <v>45</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.1192072642606282</v>
+        <v>0.04755212641183654</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.07750973284135629</v>
+        <v>0.008314770635087161</v>
       </c>
       <c r="S4" s="2" t="n">
         <v>39364</v>
@@ -2616,38 +2409,38 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>583</v>
+        <v>29</v>
       </c>
       <c r="X4" t="n">
-        <v>-55</v>
+        <v>-609</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.2100718359282402</v>
+        <v>-0.05180660636782208</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.3100613758801871</v>
+        <v>-0.07968906534569831</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>218</v>
+        <v>28</v>
       </c>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="b">
         <v>1</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.2659378985114353</v>
+        <v>0.05463717287606285</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.02076716510152961</v>
+        <v>-0.08996212730779873</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.08275397426662046</v>
+        <v>0.2410192038270386</v>
       </c>
       <c r="AH4" t="n">
-        <v>-162</v>
+        <v>-352</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -2667,7 +2460,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2698,35 +2491,35 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
         <v>36608</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>36650</v>
+        <v>37460</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>36691</v>
+        <v>37984</v>
       </c>
       <c r="M5" t="n">
-        <v>57</v>
+        <v>945</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-0.05180660636782208</v>
+        <v>-0.2761519972064159</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-0.07968906534569831</v>
+        <v>-0.3151750809469517</v>
       </c>
       <c r="P5" t="n">
-        <v>45</v>
+        <v>772</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.04755212641183654</v>
+        <v>0.1234246124375544</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0.008314770635087161</v>
+        <v>0.08715928821578969</v>
       </c>
       <c r="S5" s="2" t="n">
         <v>39364</v>
@@ -2739,38 +2532,38 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>29</v>
+        <v>583</v>
       </c>
       <c r="X5" t="n">
-        <v>-609</v>
+        <v>-55</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.05180660636782208</v>
+        <v>-0.2761519972064159</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.07968906534569831</v>
+        <v>-0.3151750809469517</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>28</v>
+        <v>362</v>
       </c>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="b">
         <v>1</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.05463717287606285</v>
+        <v>0.3815055041122559</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.08996212730779873</v>
+        <v>-0.0111176097270962</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.2410192038270386</v>
+        <v>0.01667381298844473</v>
       </c>
       <c r="AH5" t="n">
-        <v>-352</v>
+        <v>-18</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -2790,7 +2583,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2808,24 +2601,20 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
@@ -2835,25 +2624,25 @@
         <v>37460</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>37984</v>
+        <v>39064</v>
       </c>
       <c r="M6" t="n">
-        <v>945</v>
+        <v>1691</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.2761519972064159</v>
+        <v>-0.387127877918954</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.3151750809469517</v>
+        <v>-0.4201681847926452</v>
       </c>
       <c r="P6" t="n">
-        <v>772</v>
+        <v>1554</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.1234246124375544</v>
+        <v>0.2201700101841288</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.08715928821578969</v>
+        <v>0.2079336017943235</v>
       </c>
       <c r="S6" s="2" t="n">
         <v>39364</v>
@@ -2872,48 +2661,40 @@
         <v>-55</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.2761519972064159</v>
+        <v>-0.387127877918954</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.3151750809469517</v>
+        <v>-0.4201681847926452</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>362</v>
+        <v>1108</v>
       </c>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="b">
         <v>1</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.3815055041122559</v>
+        <v>0.631661751238475</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>-0.0111176097270962</v>
+        <v>0.1096567038514376</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.01667381298844473</v>
+        <v>-0.09430206772409333</v>
       </c>
       <c r="AH6" t="n">
-        <v>-18</v>
+        <v>728</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
-      <c r="AJ6" s="3" t="n">
-        <v>0.009649555374433405</v>
-      </c>
-      <c r="AK6" s="3" t="n">
-        <v>-0.06608016127817573</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>144</v>
-      </c>
-      <c r="AM6" t="b">
-        <v>0</v>
-      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
       <c r="AN6" s="3" t="inlineStr"/>
       <c r="AO6" s="3" t="inlineStr"/>
     </row>
@@ -2925,7 +2706,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2956,7 +2737,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
@@ -2966,25 +2747,25 @@
         <v>37460</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>39064</v>
+        <v>38007</v>
       </c>
       <c r="M7" t="n">
-        <v>1691</v>
+        <v>960</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>-0.387127877918954</v>
+        <v>-0.3090916103536964</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>-0.4201681847926452</v>
+        <v>-0.3463388996218203</v>
       </c>
       <c r="P7" t="n">
-        <v>1554</v>
+        <v>823</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.2201700101841288</v>
+        <v>0.1424323535440002</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.2079336017943235</v>
+        <v>0.1013763566202188</v>
       </c>
       <c r="S7" s="2" t="n">
         <v>39364</v>
@@ -3003,32 +2784,32 @@
         <v>-55</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.387127877918954</v>
+        <v>-0.3090916103536964</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.4201681847926452</v>
+        <v>-0.3463388996218203</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1108</v>
+        <v>377</v>
       </c>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="b">
         <v>1</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.631661751238475</v>
+        <v>0.4473698901122469</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>0.1096567038514376</v>
+        <v>0.003099458677332953</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>-0.09430206772409333</v>
+        <v>-0.01626580015883572</v>
       </c>
       <c r="AH7" t="n">
-        <v>728</v>
+        <v>-3</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -3048,7 +2829,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3066,52 +2847,48 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
         <v>36608</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>37460</v>
+        <v>37838</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>38007</v>
+        <v>38303</v>
       </c>
       <c r="M8" t="n">
-        <v>960</v>
+        <v>1166</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.3090916103536964</v>
+        <v>-0.1457017075496173</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.3463388996218203</v>
+        <v>-0.2055959130438868</v>
       </c>
       <c r="P8" t="n">
-        <v>823</v>
+        <v>791</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.1424323535440002</v>
+        <v>0.1216014399220798</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.1013763566202188</v>
+        <v>0.09537630211584516</v>
       </c>
       <c r="S8" s="2" t="n">
         <v>39364</v>
@@ -3124,54 +2901,46 @@
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>583</v>
+        <v>844</v>
       </c>
       <c r="X8" t="n">
-        <v>-55</v>
+        <v>206</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.3090916103536964</v>
+        <v>-0.1457017075496173</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.3463388996218203</v>
+        <v>-0.2055959130438868</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>377</v>
+        <v>322</v>
       </c>
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="b">
         <v>1</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.4473698901122469</v>
+        <v>0.1705513271385588</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>0.003099458677332953</v>
+        <v>-0.002900595827040733</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>-0.01626580015883572</v>
+        <v>0.1471241026452433</v>
       </c>
       <c r="AH8" t="n">
-        <v>-3</v>
+        <v>-58</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
-      <c r="AJ8" s="3" t="n">
-        <v>0.02386662377886256</v>
-      </c>
-      <c r="AK8" s="3" t="n">
-        <v>-0.09901977442545618</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>159</v>
-      </c>
-      <c r="AM8" t="b">
-        <v>0</v>
-      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
       <c r="AN8" s="3" t="inlineStr"/>
       <c r="AO8" s="3" t="inlineStr"/>
     </row>
@@ -3183,7 +2952,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3214,35 +2983,35 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
         <v>36608</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>37838</v>
+        <v>37460</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>38303</v>
+        <v>37986</v>
       </c>
       <c r="M9" t="n">
-        <v>1166</v>
+        <v>947</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>-0.1457017075496173</v>
+        <v>-0.2828037839281438</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.2055959130438868</v>
+        <v>-0.3401599263032039</v>
       </c>
       <c r="P9" t="n">
-        <v>791</v>
+        <v>660</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.1216014399220798</v>
+        <v>0.1418778148333315</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.09537630211584516</v>
+        <v>0.1002963190039776</v>
       </c>
       <c r="S9" s="2" t="n">
         <v>39364</v>
@@ -3255,38 +3024,38 @@
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>844</v>
+        <v>583</v>
       </c>
       <c r="X9" t="n">
-        <v>206</v>
+        <v>-55</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.1457017075496173</v>
+        <v>-0.2828037839281438</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.2055959130438868</v>
+        <v>-0.3401599263032039</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>322</v>
+        <v>364</v>
       </c>
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="b">
         <v>1</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.1705513271385588</v>
+        <v>0.3943185666498406</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.002900595827040733</v>
+        <v>0.00201942106109175</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.1471241026452433</v>
+        <v>0.01002202626671689</v>
       </c>
       <c r="AH9" t="n">
-        <v>-58</v>
+        <v>-16</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -3297,141 +3066,6 @@
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" s="3" t="inlineStr"/>
       <c r="AO9" s="3" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>hrp</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>36608</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>37460</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>37986</v>
-      </c>
-      <c r="M10" t="n">
-        <v>947</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.2828037839281438</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.3401599263032039</v>
-      </c>
-      <c r="P10" t="n">
-        <v>660</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.1418778148333315</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.1002963190039776</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>39364</v>
-      </c>
-      <c r="T10" t="b">
-        <v>0</v>
-      </c>
-      <c r="U10" t="b">
-        <v>0</v>
-      </c>
-      <c r="V10" s="3" t="inlineStr"/>
-      <c r="W10" t="n">
-        <v>583</v>
-      </c>
-      <c r="X10" t="n">
-        <v>-55</v>
-      </c>
-      <c r="Y10" s="3" t="n">
-        <v>-0.2828037839281438</v>
-      </c>
-      <c r="Z10" s="3" t="n">
-        <v>-0.3401599263032039</v>
-      </c>
-      <c r="AA10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>364</v>
-      </c>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="b">
-        <v>1</v>
-      </c>
-      <c r="AE10" s="3" t="n">
-        <v>0.3943185666498406</v>
-      </c>
-      <c r="AF10" s="3" t="n">
-        <v>0.00201942106109175</v>
-      </c>
-      <c r="AG10" s="3" t="n">
-        <v>0.01002202626671689</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>-16</v>
-      </c>
-      <c r="AI10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ10" s="3" t="n">
-        <v>0.02278658616262136</v>
-      </c>
-      <c r="AK10" s="3" t="n">
-        <v>-0.07273194799990357</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>146</v>
-      </c>
-      <c r="AM10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AN10" s="3" t="inlineStr"/>
-      <c r="AO10" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3444,7 +3078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO10"/>
+  <dimension ref="A1:AO9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3922,12 +3556,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3937,7 +3571,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -3948,41 +3582,45 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
         <v>39364</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>39881</v>
+        <v>41061</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>40486</v>
+        <v>41124</v>
       </c>
       <c r="M4" t="n">
-        <v>775</v>
+        <v>1215</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.3674998761946072</v>
+        <v>-0.09466293283795224</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.3674998761946072</v>
+        <v>-0.1506103472912015</v>
       </c>
       <c r="P4" t="n">
-        <v>774</v>
+        <v>247</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.1532547245176266</v>
+        <v>0.04847007156721702</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.08127722777506252</v>
+        <v>0.03217841127955078</v>
       </c>
       <c r="S4" s="2" t="n">
         <v>43364</v>
@@ -3995,40 +3633,40 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>355</v>
+        <v>1171</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>816</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.3674998761946072</v>
+        <v>-0.09466293283795224</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.3674998761946072</v>
+        <v>-0.1506103472912015</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>420</v>
+        <v>44</v>
       </c>
       <c r="AC4" t="n">
-        <v>-440</v>
+        <v>-816</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.5810273585142876</v>
+        <v>0.104560982060186</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.03534029360309213</v>
+        <v>-0.08443911009860386</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.07648403652350821</v>
+        <v>0.3493209798801632</v>
       </c>
       <c r="AH4" t="n">
-        <v>-179</v>
+        <v>-555</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -4037,8 +3675,12 @@
       <c r="AK4" s="3" t="inlineStr"/>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
-      <c r="AN4" s="3" t="inlineStr"/>
-      <c r="AO4" s="3" t="inlineStr"/>
+      <c r="AN4" s="3" t="n">
+        <v>0.1241816912769598</v>
+      </c>
+      <c r="AO4" s="3" t="n">
+        <v>-0.08939590726649083</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4048,7 +3690,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4079,35 +3721,35 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
         <v>39364</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>41061</v>
+        <v>39881</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>41124</v>
+        <v>40486</v>
       </c>
       <c r="M5" t="n">
-        <v>1215</v>
+        <v>775</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-0.09466293283795224</v>
+        <v>-0.3674998761946072</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-0.1506103472912015</v>
+        <v>-0.3674998761946072</v>
       </c>
       <c r="P5" t="n">
-        <v>247</v>
+        <v>774</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.04847007156721702</v>
+        <v>0.1532547245176266</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0.03217841127955078</v>
+        <v>0.08127722777506252</v>
       </c>
       <c r="S5" s="2" t="n">
         <v>43364</v>
@@ -4120,40 +3762,40 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>1171</v>
+        <v>355</v>
       </c>
       <c r="X5" t="n">
-        <v>816</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.09466293283795224</v>
+        <v>-0.3674998761946072</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.1506103472912015</v>
+        <v>-0.3674998761946072</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>44</v>
+        <v>420</v>
       </c>
       <c r="AC5" t="n">
-        <v>-816</v>
+        <v>-440</v>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.104560982060186</v>
+        <v>0.5810273585142876</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.08443911009860386</v>
+        <v>-0.03534029360309213</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.3493209798801632</v>
+        <v>0.07648403652350821</v>
       </c>
       <c r="AH5" t="n">
-        <v>-555</v>
+        <v>-179</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -4166,7 +3808,7 @@
         <v>0.1241816912769598</v>
       </c>
       <c r="AO5" s="3" t="n">
-        <v>-0.08939590726649083</v>
+        <v>0.01312838014984941</v>
       </c>
     </row>
     <row r="6">
@@ -4177,7 +3819,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -4195,24 +3837,20 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
@@ -4222,25 +3860,25 @@
         <v>39881</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>40486</v>
+        <v>40133</v>
       </c>
       <c r="M6" t="n">
-        <v>775</v>
+        <v>531</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.3674998761946072</v>
+        <v>-0.2697487878045376</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.3674998761946072</v>
+        <v>-0.2697487878045376</v>
       </c>
       <c r="P6" t="n">
-        <v>774</v>
+        <v>530</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.1532547245176266</v>
+        <v>0.0917109960363139</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.08127722777506252</v>
+        <v>0.04027183103505601</v>
       </c>
       <c r="S6" s="2" t="n">
         <v>43364</v>
@@ -4259,56 +3897,44 @@
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.3674998761946072</v>
+        <v>-0.2697487878045376</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.3674998761946072</v>
+        <v>-0.2697487878045376</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>420</v>
+        <v>176</v>
       </c>
       <c r="AC6" t="n">
-        <v>-440</v>
+        <v>-684</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.5810273585142876</v>
+        <v>0.3693917699822118</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>-0.03534029360309213</v>
+        <v>-0.07634569034309864</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.07648403652350821</v>
+        <v>0.1742351249135778</v>
       </c>
       <c r="AH6" t="n">
-        <v>-179</v>
+        <v>-423</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
-      <c r="AJ6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AN6" s="3" t="n">
-        <v>0.1241816912769598</v>
-      </c>
-      <c r="AO6" s="3" t="n">
-        <v>0.01312838014984941</v>
-      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4318,7 +3944,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4349,7 +3975,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
@@ -4359,25 +3985,25 @@
         <v>39881</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>40133</v>
+        <v>40567</v>
       </c>
       <c r="M7" t="n">
-        <v>531</v>
+        <v>829</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>-0.2697487878045376</v>
+        <v>-0.4000942896051511</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>-0.2697487878045376</v>
+        <v>-0.4000942896051511</v>
       </c>
       <c r="P7" t="n">
-        <v>530</v>
+        <v>828</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.0917109960363139</v>
+        <v>0.1700991045634237</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.04027183103505601</v>
+        <v>0.09329647245376695</v>
       </c>
       <c r="S7" s="2" t="n">
         <v>43364</v>
@@ -4396,34 +4022,34 @@
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.2697487878045376</v>
+        <v>-0.4000942896051511</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.2697487878045376</v>
+        <v>-0.4000942896051511</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>176</v>
+        <v>474</v>
       </c>
       <c r="AC7" t="n">
-        <v>-684</v>
+        <v>-386</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.3693917699822118</v>
+        <v>0.6669286234028597</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>-0.07634569034309864</v>
+        <v>-0.0233210489243877</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.1742351249135778</v>
+        <v>0.04388962311296429</v>
       </c>
       <c r="AH7" t="n">
-        <v>-423</v>
+        <v>-125</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -4443,7 +4069,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4461,52 +4087,48 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
         <v>39364</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>39881</v>
+        <v>39412</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>40567</v>
+        <v>40101</v>
       </c>
       <c r="M8" t="n">
-        <v>829</v>
+        <v>509</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.4000942896051511</v>
+        <v>-0.08264378139658068</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.4000942896051511</v>
+        <v>-0.08264378139658068</v>
       </c>
       <c r="P8" t="n">
-        <v>828</v>
+        <v>508</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.1700991045634237</v>
+        <v>0.04931580087778874</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.09329647245376695</v>
+        <v>0.02120290308064275</v>
       </c>
       <c r="S8" s="2" t="n">
         <v>43364</v>
@@ -4519,56 +4141,48 @@
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>355</v>
+        <v>33</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-322</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.4000942896051511</v>
+        <v>-0.08264378139658068</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.4000942896051511</v>
+        <v>-0.08264378139658068</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="AC8" t="n">
-        <v>-386</v>
+        <v>-384</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.6669286234028597</v>
+        <v>0.09008908395737203</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>-0.0233210489243877</v>
+        <v>-0.0954146182975119</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.04388962311296429</v>
+        <v>0.3613401313215348</v>
       </c>
       <c r="AH8" t="n">
-        <v>-125</v>
+        <v>-123</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
-      <c r="AJ8" s="3" t="n">
-        <v>0.01201924467870442</v>
-      </c>
-      <c r="AK8" s="3" t="n">
-        <v>-0.03259441341054392</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>54</v>
-      </c>
-      <c r="AM8" t="b">
-        <v>0</v>
-      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
       <c r="AN8" s="3" t="inlineStr"/>
       <c r="AO8" s="3" t="inlineStr"/>
     </row>
@@ -4580,7 +4194,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4611,35 +4225,35 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
         <v>39364</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>39412</v>
+        <v>39881</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>40101</v>
+        <v>40546</v>
       </c>
       <c r="M9" t="n">
-        <v>509</v>
+        <v>815</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>-0.08264378139658068</v>
+        <v>-0.3816212997058295</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.08264378139658068</v>
+        <v>-0.3816212997058295</v>
       </c>
       <c r="P9" t="n">
-        <v>508</v>
+        <v>814</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.04931580087778874</v>
+        <v>0.1642351393340294</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.02120290308064275</v>
+        <v>0.08931724369670038</v>
       </c>
       <c r="S9" s="2" t="n">
         <v>43364</v>
@@ -4652,40 +4266,40 @@
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>33</v>
+        <v>355</v>
       </c>
       <c r="X9" t="n">
-        <v>-322</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.08264378139658068</v>
+        <v>-0.3816212997058295</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.08264378139658068</v>
+        <v>-0.3816212997058295</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>476</v>
+        <v>460</v>
       </c>
       <c r="AC9" t="n">
-        <v>-384</v>
+        <v>-400</v>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.09008908395737203</v>
+        <v>0.6171320252852943</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.0954146182975119</v>
+        <v>-0.02730027768145427</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.3613401313215348</v>
+        <v>0.06236261301228596</v>
       </c>
       <c r="AH9" t="n">
-        <v>-123</v>
+        <v>-139</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -4696,143 +4310,6 @@
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" s="3" t="inlineStr"/>
       <c r="AO9" s="3" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>hrp</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>39364</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>40546</v>
-      </c>
-      <c r="M10" t="n">
-        <v>815</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.3816212997058295</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.3816212997058295</v>
-      </c>
-      <c r="P10" t="n">
-        <v>814</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.1642351393340294</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.08931724369670038</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>43364</v>
-      </c>
-      <c r="T10" t="b">
-        <v>0</v>
-      </c>
-      <c r="U10" t="b">
-        <v>0</v>
-      </c>
-      <c r="V10" s="3" t="inlineStr"/>
-      <c r="W10" t="n">
-        <v>355</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="3" t="n">
-        <v>-0.3816212997058295</v>
-      </c>
-      <c r="Z10" s="3" t="n">
-        <v>-0.3816212997058295</v>
-      </c>
-      <c r="AA10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>460</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>-400</v>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="3" t="n">
-        <v>0.6171320252852943</v>
-      </c>
-      <c r="AF10" s="3" t="n">
-        <v>-0.02730027768145427</v>
-      </c>
-      <c r="AG10" s="3" t="n">
-        <v>0.06236261301228596</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>-139</v>
-      </c>
-      <c r="AI10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ10" s="3" t="n">
-        <v>0.008040015921637861</v>
-      </c>
-      <c r="AK10" s="3" t="n">
-        <v>-0.01412142351122225</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AN10" s="3" t="inlineStr"/>
-      <c r="AO10" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4845,7 +4322,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO10"/>
+  <dimension ref="A1:AO9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5323,12 +4800,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -5338,7 +4815,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -5349,13 +4826,17 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
@@ -5365,25 +4846,25 @@
         <v>43458</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>43560</v>
+        <v>43537</v>
       </c>
       <c r="M4" t="n">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.1350492147242662</v>
+        <v>-0.133289881480832</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.1424709615053656</v>
+        <v>-0.1410541034597298</v>
       </c>
       <c r="P4" t="n">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.04801488482583489</v>
+        <v>0.04716738793712075</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.02965112288406209</v>
+        <v>0.02723210412246817</v>
       </c>
       <c r="S4" s="2" t="n">
         <v>43880</v>
@@ -5402,34 +4883,34 @@
         <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.1350492147242662</v>
+        <v>-0.133289881480832</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.1424709615053656</v>
+        <v>-0.1410541034597298</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="AC4" t="n">
-        <v>-6</v>
+        <v>-23</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.1561351432049565</v>
+        <v>0.1537883066469405</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>0.002205245441767464</v>
+        <v>-0.0002137733198264505</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.002895432769700834</v>
+        <v>0.004654766013135081</v>
       </c>
       <c r="AH4" t="n">
-        <v>14</v>
+        <v>-3</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -5438,8 +4919,12 @@
       <c r="AK4" s="3" t="inlineStr"/>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
-      <c r="AN4" s="3" t="inlineStr"/>
-      <c r="AO4" s="3" t="inlineStr"/>
+      <c r="AN4" s="3" t="n">
+        <v>0.1656098075061709</v>
+      </c>
+      <c r="AO4" s="3" t="n">
+        <v>-0.1340945703114591</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5449,7 +4934,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -5480,7 +4965,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
@@ -5490,25 +4975,25 @@
         <v>43458</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>43537</v>
+        <v>43542</v>
       </c>
       <c r="M5" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-0.133289881480832</v>
+        <v>-0.1391937251083381</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-0.1410541034597298</v>
+        <v>-0.1410541034597297</v>
       </c>
       <c r="P5" t="n">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.04716738793712075</v>
+        <v>0.04715558064723339</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0.02723210412246817</v>
+        <v>0.02756919917766997</v>
       </c>
       <c r="S5" s="2" t="n">
         <v>43880</v>
@@ -5527,34 +5012,34 @@
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.133289881480832</v>
+        <v>-0.1391937251083381</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.1410541034597298</v>
+        <v>-0.1410541034597297</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="AC5" t="n">
-        <v>-23</v>
+        <v>-20</v>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.1537883066469405</v>
+        <v>0.1617015688295911</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.0002137733198264505</v>
+        <v>0.0001233217353753466</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.004654766013135081</v>
+        <v>-0.001249077614370986</v>
       </c>
       <c r="AH5" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -5567,7 +5052,7 @@
         <v>0.1656098075061709</v>
       </c>
       <c r="AO5" s="3" t="n">
-        <v>-0.1340945703114591</v>
+        <v>0.009509211625454705</v>
       </c>
     </row>
     <row r="6">
@@ -5578,7 +5063,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -5596,24 +5081,20 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
@@ -5623,25 +5104,25 @@
         <v>43458</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>43542</v>
+        <v>43766</v>
       </c>
       <c r="M6" t="n">
-        <v>120</v>
+        <v>276</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.1391937251083381</v>
+        <v>-0.1379446474939671</v>
       </c>
       <c r="O6" s="3" t="n">
         <v>-0.1410541034597297</v>
       </c>
       <c r="P6" t="n">
-        <v>116</v>
+        <v>272</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.04715558064723339</v>
+        <v>0.05865945403888815</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.02756919917766997</v>
+        <v>0.05188911577288446</v>
       </c>
       <c r="S6" s="2" t="n">
         <v>43880</v>
@@ -5660,7 +5141,7 @@
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.1391937251083381</v>
+        <v>-0.1379446474939671</v>
       </c>
       <c r="Z6" s="3" t="n">
         <v>-0.1410541034597297</v>
@@ -5669,47 +5150,35 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>56</v>
+        <v>212</v>
       </c>
       <c r="AC6" t="n">
-        <v>-20</v>
+        <v>136</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.1617015688295911</v>
+        <v>0.1600183179571426</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>0.0001233217353753466</v>
+        <v>0.02444323833058984</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>-0.001249077614370986</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
-      <c r="AJ6" s="3" t="n">
-        <v>-0.002081923706392118</v>
-      </c>
-      <c r="AK6" s="3" t="n">
-        <v>-0.00414451038407182</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>-14</v>
-      </c>
-      <c r="AM6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AN6" s="3" t="n">
-        <v>0.1656098075061709</v>
-      </c>
-      <c r="AO6" s="3" t="n">
-        <v>0.009509211625454705</v>
-      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5719,7 +5188,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -5750,7 +5219,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
@@ -5760,10 +5229,10 @@
         <v>43458</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>43766</v>
+        <v>43559</v>
       </c>
       <c r="M7" t="n">
-        <v>276</v>
+        <v>133</v>
       </c>
       <c r="N7" s="3" t="n">
         <v>-0.1379446474939671</v>
@@ -5772,13 +5241,13 @@
         <v>-0.1410541034597297</v>
       </c>
       <c r="P7" t="n">
-        <v>272</v>
+        <v>129</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.05865945403888815</v>
+        <v>0.04619261644745546</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.05188911577288446</v>
+        <v>0.02841995137059498</v>
       </c>
       <c r="S7" s="2" t="n">
         <v>43880</v>
@@ -5806,10 +5275,10 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>212</v>
+        <v>69</v>
       </c>
       <c r="AC7" t="n">
-        <v>136</v>
+        <v>-7</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
@@ -5818,13 +5287,13 @@
         <v>0.1600183179571426</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>0.02444323833058984</v>
+        <v>0.0009740739283003591</v>
       </c>
       <c r="AG7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>156</v>
+        <v>13</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -5844,7 +5313,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -5862,24 +5331,20 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
@@ -5889,25 +5354,25 @@
         <v>43458</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>43559</v>
+        <v>43766</v>
       </c>
       <c r="M8" t="n">
-        <v>133</v>
+        <v>276</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.1379446474939671</v>
+        <v>-0.1379446474939672</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.1410541034597297</v>
+        <v>-0.1410541034597296</v>
       </c>
       <c r="P8" t="n">
-        <v>129</v>
+        <v>272</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.04619261644745546</v>
+        <v>0.0586594540388882</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.02841995137059498</v>
+        <v>0.05188911577288451</v>
       </c>
       <c r="S8" s="2" t="n">
         <v>43880</v>
@@ -5926,50 +5391,42 @@
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.1379446474939671</v>
+        <v>-0.1379446474939672</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.1410541034597297</v>
+        <v>-0.1410541034597296</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>69</v>
+        <v>212</v>
       </c>
       <c r="AC8" t="n">
-        <v>-7</v>
+        <v>136</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.1600183179571426</v>
+        <v>0.1600183179571428</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>0.0009740739283003591</v>
+        <v>0.02444323833058989</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0</v>
+        <v>-1.110223024625157e-16</v>
       </c>
       <c r="AH8" t="n">
-        <v>13</v>
+        <v>156</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
-      <c r="AJ8" s="3" t="n">
-        <v>-0.001231171513467105</v>
-      </c>
-      <c r="AK8" s="3" t="n">
-        <v>-0.002895432769700834</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AM8" t="b">
-        <v>0</v>
-      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
       <c r="AN8" s="3" t="inlineStr"/>
       <c r="AO8" s="3" t="inlineStr"/>
     </row>
@@ -5981,7 +5438,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -6012,7 +5469,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
@@ -6022,25 +5479,25 @@
         <v>43458</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>43766</v>
+        <v>43559</v>
       </c>
       <c r="M9" t="n">
-        <v>276</v>
+        <v>133</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>-0.1379446474939672</v>
+        <v>-0.1379446474939671</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.1410541034597296</v>
+        <v>-0.1410541034597297</v>
       </c>
       <c r="P9" t="n">
-        <v>272</v>
+        <v>129</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.0586594540388882</v>
+        <v>0.04619261644745546</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.05188911577288451</v>
+        <v>0.02841995137059498</v>
       </c>
       <c r="S9" s="2" t="n">
         <v>43880</v>
@@ -6059,34 +5516,34 @@
         <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.1379446474939672</v>
+        <v>-0.1379446474939671</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.1410541034597296</v>
+        <v>-0.1410541034597297</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>212</v>
+        <v>69</v>
       </c>
       <c r="AC9" t="n">
-        <v>136</v>
+        <v>-7</v>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.1600183179571428</v>
+        <v>0.1600183179571426</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>0.02444323833058989</v>
+        <v>0.0009740739283003591</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>-1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>156</v>
+        <v>13</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -6097,143 +5554,6 @@
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" s="3" t="inlineStr"/>
       <c r="AO9" s="3" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>hrp</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>43364</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>43458</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>43559</v>
-      </c>
-      <c r="M10" t="n">
-        <v>133</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.1379446474939671</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.1410541034597297</v>
-      </c>
-      <c r="P10" t="n">
-        <v>129</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.04619261644745546</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.02841995137059498</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>43880</v>
-      </c>
-      <c r="T10" t="b">
-        <v>0</v>
-      </c>
-      <c r="U10" t="b">
-        <v>0</v>
-      </c>
-      <c r="V10" s="3" t="inlineStr"/>
-      <c r="W10" t="n">
-        <v>64</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="3" t="n">
-        <v>-0.1379446474939671</v>
-      </c>
-      <c r="Z10" s="3" t="n">
-        <v>-0.1410541034597297</v>
-      </c>
-      <c r="AA10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>69</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>-7</v>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="3" t="n">
-        <v>0.1600183179571426</v>
-      </c>
-      <c r="AF10" s="3" t="n">
-        <v>0.0009740739283003591</v>
-      </c>
-      <c r="AG10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>13</v>
-      </c>
-      <c r="AI10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ10" s="3" t="n">
-        <v>-0.001231171513467105</v>
-      </c>
-      <c r="AK10" s="3" t="n">
-        <v>-0.002895432769700834</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AM10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AN10" s="3" t="inlineStr"/>
-      <c r="AO10" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6246,7 +5566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO10"/>
+  <dimension ref="A1:AO9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6724,12 +6044,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -6739,7 +6059,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -6750,13 +6070,17 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
@@ -6765,26 +6089,24 @@
       <c r="K4" s="2" t="n">
         <v>43913</v>
       </c>
-      <c r="L4" s="2" t="n">
-        <v>44055</v>
-      </c>
+      <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>122</v>
+        <v>473</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.2845422957875736</v>
+        <v>-0.290246477182812</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.2845422957875736</v>
+        <v>-0.290246477182812</v>
       </c>
       <c r="P4" t="n">
-        <v>121</v>
+        <v>473</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.1140968231800305</v>
+        <v>0.2207358717089996</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.05812151649835226</v>
+        <v>0.2207358717089996</v>
       </c>
       <c r="S4" s="2" t="n">
         <v>44564</v>
@@ -6793,9 +6115,11 @@
         <v>0</v>
       </c>
       <c r="U4" t="b">
-        <v>0</v>
-      </c>
-      <c r="V4" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V4" s="3" t="n">
+        <v>-0.2234811907476071</v>
+      </c>
       <c r="W4" t="n">
         <v>23</v>
       </c>
@@ -6803,37 +6127,33 @@
         <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.2845422957875736</v>
+        <v>-0.290246477182812</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.2845422957875736</v>
+        <v>-0.290246477182812</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>99</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>44</v>
-      </c>
+        <v>450</v>
+      </c>
+      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.3977066626192765</v>
+        <v>0.4089398190385187</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.001375730934979565</v>
+        <v>0.1612386242756678</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.005704181395238317</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
+        <v>-1.110223024625157e-16</v>
+      </c>
+      <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ4" s="3" t="inlineStr"/>
       <c r="AK4" s="3" t="inlineStr"/>
@@ -6850,7 +6170,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -6881,7 +6201,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
@@ -6890,24 +6210,26 @@
       <c r="K5" s="2" t="n">
         <v>43913</v>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="n">
+        <v>44069</v>
+      </c>
       <c r="M5" t="n">
-        <v>473</v>
+        <v>132</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-0.290246477182812</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-0.290246477182812</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="P5" t="n">
-        <v>473</v>
+        <v>131</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.2207358717089996</v>
+        <v>0.1201318255357319</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0.2207358717089996</v>
+        <v>0.06363480628085999</v>
       </c>
       <c r="S5" s="2" t="n">
         <v>44564</v>
@@ -6916,11 +6238,9 @@
         <v>0</v>
       </c>
       <c r="U5" t="b">
-        <v>1</v>
-      </c>
-      <c r="V5" s="3" t="n">
-        <v>-0.2234811907476071</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
         <v>23</v>
       </c>
@@ -6928,33 +6248,37 @@
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.290246477182812</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.290246477182812</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>450</v>
-      </c>
-      <c r="AC5" t="inlineStr"/>
+        <v>109</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>54</v>
+      </c>
       <c r="AD5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.4089398190385187</v>
+        <v>0.4089398190385185</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>0.1612386242756678</v>
+        <v>0.004137558847528165</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>-1.110223024625157e-16</v>
-      </c>
-      <c r="AH5" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>10</v>
+      </c>
       <c r="AI5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ5" s="3" t="inlineStr"/>
       <c r="AK5" s="3" t="inlineStr"/>
@@ -6971,7 +6295,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -6989,24 +6313,20 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
@@ -7016,10 +6336,10 @@
         <v>43913</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>44069</v>
+        <v>44503</v>
       </c>
       <c r="M6" t="n">
-        <v>132</v>
+        <v>432</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>-0.2902464771828119</v>
@@ -7028,13 +6348,13 @@
         <v>-0.2902464771828119</v>
       </c>
       <c r="P6" t="n">
-        <v>131</v>
+        <v>431</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.1201318255357319</v>
+        <v>0.1610753648867642</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.06363480628085999</v>
+        <v>0.153951491648402</v>
       </c>
       <c r="S6" s="2" t="n">
         <v>44564</v>
@@ -7062,10 +6382,10 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>109</v>
+        <v>409</v>
       </c>
       <c r="AC6" t="n">
-        <v>54</v>
+        <v>354</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
@@ -7074,29 +6394,21 @@
         <v>0.4089398190385185</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>0.004137558847528165</v>
+        <v>0.09445424421507018</v>
       </c>
       <c r="AG6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>10</v>
+        <v>310</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
-      <c r="AJ6" s="3" t="n">
-        <v>0.00551328978250773</v>
-      </c>
-      <c r="AK6" s="3" t="n">
-        <v>-0.005704181395238317</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AM6" t="b">
-        <v>0</v>
-      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
       <c r="AN6" s="3" t="inlineStr"/>
       <c r="AO6" s="3" t="inlineStr"/>
     </row>
@@ -7108,7 +6420,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -7139,7 +6451,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
@@ -7149,10 +6461,10 @@
         <v>43913</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>44503</v>
+        <v>44069</v>
       </c>
       <c r="M7" t="n">
-        <v>432</v>
+        <v>132</v>
       </c>
       <c r="N7" s="3" t="n">
         <v>-0.2902464771828119</v>
@@ -7161,13 +6473,13 @@
         <v>-0.2902464771828119</v>
       </c>
       <c r="P7" t="n">
-        <v>431</v>
+        <v>131</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.1610753648867642</v>
+        <v>0.1201318255357319</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.153951491648402</v>
+        <v>0.06363480628085999</v>
       </c>
       <c r="S7" s="2" t="n">
         <v>44564</v>
@@ -7195,10 +6507,10 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>409</v>
+        <v>109</v>
       </c>
       <c r="AC7" t="n">
-        <v>354</v>
+        <v>54</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
@@ -7207,13 +6519,13 @@
         <v>0.4089398190385185</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>0.09445424421507018</v>
+        <v>0.004137558847528165</v>
       </c>
       <c r="AG7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>310</v>
+        <v>10</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -7233,7 +6545,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -7251,24 +6563,20 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
@@ -7277,26 +6585,24 @@
       <c r="K8" s="2" t="n">
         <v>43913</v>
       </c>
-      <c r="L8" s="2" t="n">
-        <v>44069</v>
-      </c>
+      <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>132</v>
+        <v>473</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.2902464771828118</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.2902464771828118</v>
       </c>
       <c r="P8" t="n">
-        <v>131</v>
+        <v>473</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.1201318255357319</v>
+        <v>0.1998307842766896</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.06363480628085999</v>
+        <v>0.1998307842766896</v>
       </c>
       <c r="S8" s="2" t="n">
         <v>44564</v>
@@ -7305,9 +6611,11 @@
         <v>0</v>
       </c>
       <c r="U8" t="b">
-        <v>0</v>
-      </c>
-      <c r="V8" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V8" s="3" t="n">
+        <v>-0.1772797824616827</v>
+      </c>
       <c r="W8" t="n">
         <v>23</v>
       </c>
@@ -7315,50 +6623,38 @@
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.2902464771828118</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.2902464771828118</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>109</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>54</v>
-      </c>
+        <v>450</v>
+      </c>
+      <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.4089398190385185</v>
+        <v>0.4089398190385183</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>0.004137558847528165</v>
+        <v>0.1403335368433578</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>10</v>
-      </c>
+        <v>1.110223024625157e-16</v>
+      </c>
+      <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ8" s="3" t="n">
-        <v>0.00551328978250773</v>
-      </c>
-      <c r="AK8" s="3" t="n">
-        <v>-0.005704181395238317</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AM8" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
       <c r="AN8" s="3" t="inlineStr"/>
       <c r="AO8" s="3" t="inlineStr"/>
     </row>
@@ -7370,7 +6666,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -7401,7 +6697,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
@@ -7410,24 +6706,26 @@
       <c r="K9" s="2" t="n">
         <v>43913</v>
       </c>
-      <c r="L9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="n">
+        <v>44069</v>
+      </c>
       <c r="M9" t="n">
-        <v>473</v>
+        <v>132</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>-0.2902464771828118</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.2902464771828118</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="P9" t="n">
-        <v>473</v>
+        <v>131</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.1998307842766896</v>
+        <v>0.1201318255357319</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.1998307842766896</v>
+        <v>0.06363480628085999</v>
       </c>
       <c r="S9" s="2" t="n">
         <v>44564</v>
@@ -7436,11 +6734,9 @@
         <v>0</v>
       </c>
       <c r="U9" t="b">
-        <v>1</v>
-      </c>
-      <c r="V9" s="3" t="n">
-        <v>-0.1772797824616827</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
         <v>23</v>
       </c>
@@ -7448,33 +6744,37 @@
         <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.2902464771828118</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.2902464771828118</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>450</v>
-      </c>
-      <c r="AC9" t="inlineStr"/>
+        <v>109</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>54</v>
+      </c>
       <c r="AD9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.4089398190385183</v>
+        <v>0.4089398190385185</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>0.1403335368433578</v>
+        <v>0.004137558847528165</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>1.110223024625157e-16</v>
-      </c>
-      <c r="AH9" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>10</v>
+      </c>
       <c r="AI9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ9" s="3" t="inlineStr"/>
       <c r="AK9" s="3" t="inlineStr"/>
@@ -7482,143 +6782,6 @@
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" s="3" t="inlineStr"/>
       <c r="AO9" s="3" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>hrp</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>43880</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>44069</v>
-      </c>
-      <c r="M10" t="n">
-        <v>132</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.2902464771828119</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.2902464771828119</v>
-      </c>
-      <c r="P10" t="n">
-        <v>131</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.1201318255357319</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.06363480628085999</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>44564</v>
-      </c>
-      <c r="T10" t="b">
-        <v>0</v>
-      </c>
-      <c r="U10" t="b">
-        <v>0</v>
-      </c>
-      <c r="V10" s="3" t="inlineStr"/>
-      <c r="W10" t="n">
-        <v>23</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="3" t="n">
-        <v>-0.2902464771828119</v>
-      </c>
-      <c r="Z10" s="3" t="n">
-        <v>-0.2902464771828119</v>
-      </c>
-      <c r="AA10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>109</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>54</v>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="3" t="n">
-        <v>0.4089398190385185</v>
-      </c>
-      <c r="AF10" s="3" t="n">
-        <v>0.004137558847528165</v>
-      </c>
-      <c r="AG10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>10</v>
-      </c>
-      <c r="AI10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ10" s="3" t="n">
-        <v>0.00551328978250773</v>
-      </c>
-      <c r="AK10" s="3" t="n">
-        <v>-0.005704181395238317</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>10</v>
-      </c>
-      <c r="AM10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AN10" s="3" t="inlineStr"/>
-      <c r="AO10" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7631,7 +6794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO10"/>
+  <dimension ref="A1:AO9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8109,12 +7272,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -8124,7 +7287,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -8135,41 +7298,45 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
         <v>44564</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>44729</v>
+        <v>44846</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>45316</v>
+        <v>45324</v>
       </c>
       <c r="M4" t="n">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.2217386103320992</v>
+        <v>-0.205546354512773</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.2217386103320992</v>
+        <v>-0.2093348703683601</v>
       </c>
       <c r="P4" t="n">
-        <v>516</v>
+        <v>460</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.1197495450449226</v>
+        <v>0.1077262400995233</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.09727560120458689</v>
+        <v>0.0880141131584852</v>
       </c>
       <c r="S4" s="2" t="n">
         <v>45707</v>
@@ -8182,40 +7349,40 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>115</v>
+        <v>195</v>
       </c>
       <c r="X4" t="n">
-        <v>-80</v>
+        <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.2217386103320992</v>
+        <v>-0.205546354512773</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.2217386103320992</v>
+        <v>-0.2093348703683601</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>402</v>
+        <v>328</v>
       </c>
       <c r="AC4" t="n">
-        <v>182</v>
+        <v>108</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.2849153424233462</v>
+        <v>0.2587266805059651</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>0.005174571006752365</v>
+        <v>-0.004086917039349325</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.01592223728626674</v>
+        <v>0.03211449310559289</v>
       </c>
       <c r="AH4" t="n">
-        <v>208</v>
+        <v>134</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -8224,8 +7391,12 @@
       <c r="AK4" s="3" t="inlineStr"/>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
-      <c r="AN4" s="3" t="inlineStr"/>
-      <c r="AO4" s="3" t="inlineStr"/>
+      <c r="AN4" s="3" t="n">
+        <v>0.678953431147129</v>
+      </c>
+      <c r="AO4" s="3" t="n">
+        <v>-0.4035884689523094</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8235,7 +7406,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -8266,7 +7437,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
@@ -8276,25 +7447,25 @@
         <v>44846</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>45324</v>
+        <v>45314</v>
       </c>
       <c r="M5" t="n">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-0.205546354512773</v>
+        <v>-0.2378794616385039</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-0.2093348703683601</v>
+        <v>-0.2378794616385039</v>
       </c>
       <c r="P5" t="n">
-        <v>460</v>
+        <v>514</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.1077262400995233</v>
+        <v>0.1252414432874815</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0.0880141131584852</v>
+        <v>0.1015402167775275</v>
       </c>
       <c r="S5" s="2" t="n">
         <v>45707</v>
@@ -8313,34 +7484,34 @@
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.205546354512773</v>
+        <v>-0.2378794616385039</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.2093348703683601</v>
+        <v>-0.2378794616385039</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="AC5" t="n">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.2587266805059651</v>
+        <v>0.3121283965787454</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.004086917039349325</v>
+        <v>0.009439186579693018</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.03211449310559289</v>
+        <v>-0.0002186140201380082</v>
       </c>
       <c r="AH5" t="n">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -8353,7 +7524,7 @@
         <v>0.678953431147129</v>
       </c>
       <c r="AO5" s="3" t="n">
-        <v>-0.4035884689523094</v>
+        <v>-0.04772872481844626</v>
       </c>
     </row>
     <row r="6">
@@ -8364,7 +7535,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -8382,52 +7553,48 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
         <v>44564</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>44846</v>
+        <v>44628</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>45314</v>
+        <v>45029</v>
       </c>
       <c r="M6" t="n">
-        <v>515</v>
+        <v>320</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.2378794616385039</v>
+        <v>-0.1215847395419751</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.2378794616385039</v>
+        <v>-0.1215847395419751</v>
       </c>
       <c r="P6" t="n">
-        <v>514</v>
+        <v>319</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.1252414432874815</v>
+        <v>0.04091496331720496</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.1015402167775275</v>
+        <v>0.02616374176240441</v>
       </c>
       <c r="S6" s="2" t="n">
         <v>45707</v>
@@ -8440,62 +7607,50 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>195</v>
+        <v>44</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-151</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.2378794616385039</v>
+        <v>-0.1215847395419751</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.2378794616385039</v>
+        <v>-0.1215847395419751</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>320</v>
+        <v>276</v>
       </c>
       <c r="AC6" t="n">
-        <v>100</v>
+        <v>56</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.3121283965787454</v>
+        <v>0.1384137378016159</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>0.009439186579693018</v>
+        <v>-0.06593728843543012</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>-0.0002186140201380082</v>
+        <v>0.1160761080763908</v>
       </c>
       <c r="AH6" t="n">
-        <v>126</v>
+        <v>82</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
-      <c r="AJ6" s="3" t="n">
-        <v>0.004264615572940653</v>
-      </c>
-      <c r="AK6" s="3" t="n">
-        <v>-0.01614085130640475</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>-82</v>
-      </c>
-      <c r="AM6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AN6" s="3" t="n">
-        <v>0.678953431147129</v>
-      </c>
-      <c r="AO6" s="3" t="n">
-        <v>-0.04772872481844626</v>
-      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8505,7 +7660,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -8536,35 +7691,35 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
         <v>44564</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>44628</v>
+        <v>44729</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>45029</v>
+        <v>45299</v>
       </c>
       <c r="M7" t="n">
-        <v>320</v>
+        <v>505</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>-0.1215847395419751</v>
+        <v>-0.222104966978485</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>-0.1215847395419751</v>
+        <v>-0.222104966978485</v>
       </c>
       <c r="P7" t="n">
-        <v>319</v>
+        <v>504</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.04091496331720496</v>
+        <v>0.1197453439464034</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.02616374176240441</v>
+        <v>0.09613888164566577</v>
       </c>
       <c r="S7" s="2" t="n">
         <v>45707</v>
@@ -8577,40 +7732,40 @@
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="X7" t="n">
-        <v>-151</v>
+        <v>-80</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.1215847395419751</v>
+        <v>-0.222104966978485</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.1215847395419751</v>
+        <v>-0.222104966978485</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>276</v>
+        <v>390</v>
       </c>
       <c r="AC7" t="n">
-        <v>56</v>
+        <v>170</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.1384137378016159</v>
+        <v>0.2855204848342849</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>-0.06593728843543012</v>
+        <v>0.004037851447831239</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.1160761080763908</v>
+        <v>0.01555588063988089</v>
       </c>
       <c r="AH7" t="n">
-        <v>82</v>
+        <v>196</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -8630,7 +7785,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -8648,116 +7803,104 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
         <v>44564</v>
       </c>
-      <c r="K8" s="2" t="n">
-        <v>44729</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>45299</v>
-      </c>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.222104966978485</v>
+        <v>0</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.222104966978485</v>
+        <v>-0.07741687217408422</v>
       </c>
       <c r="P8" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.1197453439464034</v>
+        <v>0.01276474919454059</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.09613888164566577</v>
+        <v>0</v>
       </c>
       <c r="S8" s="2" t="n">
         <v>45707</v>
       </c>
       <c r="T8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U8" t="b">
         <v>0</v>
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-80</v>
+        <v>-195</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.222104966978485</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.222104966978485</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>390</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>170</v>
+        <v>-220</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.2855204848342849</v>
+        <v>0</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>0.004037851447831239</v>
+        <v>-0.09210103019783453</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.01555588063988089</v>
+        <v>0.2376608476183659</v>
       </c>
       <c r="AH8" t="n">
-        <v>196</v>
+        <v>-194</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
-      <c r="AJ8" s="3" t="n">
-        <v>-0.001136719558921126</v>
-      </c>
-      <c r="AK8" s="3" t="n">
-        <v>-0.0003663566463858459</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>-12</v>
-      </c>
-      <c r="AM8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AN8" s="3" t="inlineStr"/>
-      <c r="AO8" s="3" t="inlineStr"/>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" s="3" t="n">
+        <v>0.09967003453281076</v>
+      </c>
+      <c r="AO8" s="3" t="n">
+        <v>-0.09051009422763445</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8767,7 +7910,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -8798,77 +7941,81 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
         <v>44564</v>
       </c>
-      <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="n">
+        <v>44729</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>45310</v>
+      </c>
       <c r="M9" t="n">
         <v>513</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>0</v>
+        <v>-0.2217386103320992</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.07741687217408422</v>
+        <v>-0.2217386103320992</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>512</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.01276474919454059</v>
+        <v>0.120308212821147</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0</v>
+        <v>0.09735135630629647</v>
       </c>
       <c r="S9" s="2" t="n">
         <v>45707</v>
       </c>
       <c r="T9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U9" t="b">
         <v>0</v>
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="X9" t="n">
-        <v>-195</v>
+        <v>-80</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>0</v>
+        <v>-0.2217386103320992</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>0</v>
+        <v>-0.2217386103320992</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
       <c r="AC9" t="n">
-        <v>-220</v>
+        <v>178</v>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0</v>
+        <v>0.2849153424233462</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.09210103019783453</v>
+        <v>0.005250326108461947</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.2376608476183659</v>
+        <v>0.01592223728626674</v>
       </c>
       <c r="AH9" t="n">
-        <v>-194</v>
+        <v>204</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -8881,147 +8028,6 @@
         <v>0.09967003453281076</v>
       </c>
       <c r="AO9" s="3" t="n">
-        <v>-0.09051009422763445</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>hrp</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>44564</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>44729</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>45310</v>
-      </c>
-      <c r="M10" t="n">
-        <v>513</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.2217386103320992</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.2217386103320992</v>
-      </c>
-      <c r="P10" t="n">
-        <v>512</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.120308212821147</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.09735135630629647</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>45707</v>
-      </c>
-      <c r="T10" t="b">
-        <v>0</v>
-      </c>
-      <c r="U10" t="b">
-        <v>0</v>
-      </c>
-      <c r="V10" s="3" t="inlineStr"/>
-      <c r="W10" t="n">
-        <v>115</v>
-      </c>
-      <c r="X10" t="n">
-        <v>-80</v>
-      </c>
-      <c r="Y10" s="3" t="n">
-        <v>-0.2217386103320992</v>
-      </c>
-      <c r="Z10" s="3" t="n">
-        <v>-0.2217386103320992</v>
-      </c>
-      <c r="AA10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>398</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>178</v>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="3" t="n">
-        <v>0.2849153424233462</v>
-      </c>
-      <c r="AF10" s="3" t="n">
-        <v>0.005250326108461947</v>
-      </c>
-      <c r="AG10" s="3" t="n">
-        <v>0.01592223728626674</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>204</v>
-      </c>
-      <c r="AI10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ10" s="3" t="n">
-        <v>7.5755101709582e-05</v>
-      </c>
-      <c r="AK10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AM10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AN10" s="3" t="n">
-        <v>0.09967003453281076</v>
-      </c>
-      <c r="AO10" s="3" t="n">
         <v>-0.001640172913999871</v>
       </c>
     </row>
@@ -9036,7 +8042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO10"/>
+  <dimension ref="A1:AO9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9514,12 +8520,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -9529,7 +8535,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -9540,87 +8546,87 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
         <v>45707</v>
       </c>
-      <c r="K4" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>45911</v>
-      </c>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>141</v>
+        <v>88</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.1245530606971786</v>
+        <v>0</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.1245530606971786</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.06042568392595738</v>
+        <v>0</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.0487682868766525</v>
+        <v>0</v>
       </c>
       <c r="S4" s="2" t="n">
         <v>46021</v>
       </c>
       <c r="T4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U4" t="b">
         <v>0</v>
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-34</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.1245530606971786</v>
+        <v>0</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.1245530606971786</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>52</v>
+        <v>-55</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.1422736834243419</v>
+        <v>0</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.001561406441557986</v>
+        <v>-0.05032969331821049</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.02957125224090817</v>
+        <v>0.1541243129380868</v>
       </c>
       <c r="AH4" t="n">
-        <v>5</v>
+        <v>-102</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -9629,8 +8635,12 @@
       <c r="AK4" s="3" t="inlineStr"/>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
-      <c r="AN4" s="3" t="inlineStr"/>
-      <c r="AO4" s="3" t="inlineStr"/>
+      <c r="AN4" s="3" t="n">
+        <v>0.10904401508735</v>
+      </c>
+      <c r="AO4" s="3" t="n">
+        <v>-0.08356097205346547</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -9640,7 +8650,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -9671,77 +8681,81 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
         <v>45707</v>
       </c>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>45911</v>
+      </c>
       <c r="M5" t="n">
-        <v>88</v>
+        <v>141</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>0</v>
+        <v>-0.1245530606971789</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>0</v>
+        <v>-0.1245530606971789</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0</v>
+        <v>0.0604256839259576</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0</v>
+        <v>0.04876828687665268</v>
       </c>
       <c r="S5" s="2" t="n">
         <v>46021</v>
       </c>
       <c r="T5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="X5" t="n">
-        <v>-34</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0</v>
+        <v>-0.1245530606971789</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>0</v>
+        <v>-0.1245530606971789</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="AC5" t="n">
-        <v>-55</v>
+        <v>52</v>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0</v>
+        <v>0.1422736834243421</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.05032969331821049</v>
+        <v>-0.001561406441557806</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.1541243129380868</v>
+        <v>0.02957125224090795</v>
       </c>
       <c r="AH5" t="n">
-        <v>-102</v>
+        <v>5</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -9754,7 +8768,7 @@
         <v>0.10904401508735</v>
       </c>
       <c r="AO5" s="3" t="n">
-        <v>-0.08356097205346547</v>
+        <v>-0.03077953492302243</v>
       </c>
     </row>
     <row r="6">
@@ -9765,7 +8779,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -9783,119 +8797,103 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
         <v>45707</v>
       </c>
-      <c r="K6" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>45911</v>
-      </c>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>141</v>
+        <v>88</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.1245530606971789</v>
+        <v>-0.004757784175502544</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.1245530606971789</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.0604256839259576</v>
+        <v>0</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.04876828687665268</v>
+        <v>0</v>
       </c>
       <c r="S6" s="2" t="n">
         <v>46021</v>
       </c>
       <c r="T6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-34</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.1245530606971789</v>
+        <v>-0.004757784175502544</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.1245530606971789</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>52</v>
+        <v>-55</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.1422736834243421</v>
+        <v>0</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>-0.001561406441557806</v>
+        <v>-0.05032969331821049</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.02957125224090795</v>
+        <v>0.1493665287625843</v>
       </c>
       <c r="AH6" t="n">
-        <v>5</v>
+        <v>-102</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
-      <c r="AJ6" s="3" t="n">
-        <v>1.804112415015879e-16</v>
-      </c>
-      <c r="AK6" s="3" t="n">
-        <v>-2.220446049250313e-16</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="b">
-        <v>0</v>
-      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
       <c r="AN6" s="3" t="n">
-        <v>0.10904401508735</v>
+        <v>0.06587707306593193</v>
       </c>
       <c r="AO6" s="3" t="n">
-        <v>-0.03077953492302243</v>
+        <v>-0.05707000491572445</v>
       </c>
     </row>
     <row r="7">
@@ -9906,7 +8904,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -9937,77 +8935,81 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
         <v>45707</v>
       </c>
-      <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>45909</v>
+      </c>
       <c r="M7" t="n">
-        <v>88</v>
+        <v>139</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>-0.004757784175502544</v>
+        <v>-0.1245530606971789</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>0</v>
+        <v>-0.1245530606971789</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0</v>
+        <v>0.05718565405934494</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0</v>
+        <v>0.04582715153221364</v>
       </c>
       <c r="S7" s="2" t="n">
         <v>46021</v>
       </c>
       <c r="T7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="X7" t="n">
-        <v>-34</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.004757784175502544</v>
+        <v>-0.1245530606971789</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>0</v>
+        <v>-0.1245530606971789</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="AC7" t="n">
-        <v>-55</v>
+        <v>50</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0</v>
+        <v>0.1422736834243421</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>-0.05032969331821049</v>
+        <v>-0.00450254178599685</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.1493665287625843</v>
+        <v>0.02957125224090795</v>
       </c>
       <c r="AH7" t="n">
-        <v>-102</v>
+        <v>3</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -10020,7 +9022,7 @@
         <v>0.06587707306593193</v>
       </c>
       <c r="AO7" s="3" t="n">
-        <v>-0.05707000491572445</v>
+        <v>0.002524249698548031</v>
       </c>
     </row>
     <row r="8">
@@ -10031,7 +9033,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -10049,119 +9051,103 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
         <v>45707</v>
       </c>
-      <c r="K8" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>45909</v>
-      </c>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>139</v>
+        <v>88</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.1245530606971789</v>
+        <v>-0.004757784175502544</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.1245530606971789</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>138</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.05718565405934494</v>
+        <v>0</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.04582715153221364</v>
+        <v>0</v>
       </c>
       <c r="S8" s="2" t="n">
         <v>46021</v>
       </c>
       <c r="T8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U8" t="b">
         <v>0</v>
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-34</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.1245530606971789</v>
+        <v>-0.004757784175502544</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.1245530606971789</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>50</v>
+        <v>-55</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.1422736834243421</v>
+        <v>0</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>-0.00450254178599685</v>
+        <v>-0.05032969331821049</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.02957125224090795</v>
+        <v>0.1493665287625843</v>
       </c>
       <c r="AH8" t="n">
-        <v>3</v>
+        <v>-102</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
-      <c r="AJ8" s="3" t="n">
-        <v>-0.002941135344438864</v>
-      </c>
-      <c r="AK8" s="3" t="n">
-        <v>-2.220446049250313e-16</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AM8" t="b">
-        <v>0</v>
-      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
       <c r="AN8" s="3" t="n">
-        <v>0.06587707306593193</v>
+        <v>0.10904401508735</v>
       </c>
       <c r="AO8" s="3" t="n">
-        <v>0.002524249698548031</v>
+        <v>-0.08356097205346547</v>
       </c>
     </row>
     <row r="9">
@@ -10172,7 +9158,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -10203,77 +9189,81 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
         <v>45707</v>
       </c>
-      <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>45909</v>
+      </c>
       <c r="M9" t="n">
-        <v>88</v>
+        <v>139</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>-0.004757784175502544</v>
+        <v>-0.1245530606971789</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>0</v>
+        <v>-0.1245530606971789</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0</v>
+        <v>0.05718565405934494</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0</v>
+        <v>0.04582715153221364</v>
       </c>
       <c r="S9" s="2" t="n">
         <v>46021</v>
       </c>
       <c r="T9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U9" t="b">
         <v>0</v>
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="X9" t="n">
-        <v>-34</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.004757784175502544</v>
+        <v>-0.1245530606971789</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>0</v>
+        <v>-0.1245530606971789</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="AC9" t="n">
-        <v>-55</v>
+        <v>50</v>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0</v>
+        <v>0.1422736834243421</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.05032969331821049</v>
+        <v>-0.00450254178599685</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.1493665287625843</v>
+        <v>0.02957125224090795</v>
       </c>
       <c r="AH9" t="n">
-        <v>-102</v>
+        <v>3</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -10286,147 +9276,6 @@
         <v>0.10904401508735</v>
       </c>
       <c r="AO9" s="3" t="n">
-        <v>-0.08356097205346547</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>hrp</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>45707</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>45909</v>
-      </c>
-      <c r="M10" t="n">
-        <v>139</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.1245530606971789</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.1245530606971789</v>
-      </c>
-      <c r="P10" t="n">
-        <v>138</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.05718565405934494</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.04582715153221364</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>46021</v>
-      </c>
-      <c r="T10" t="b">
-        <v>0</v>
-      </c>
-      <c r="U10" t="b">
-        <v>0</v>
-      </c>
-      <c r="V10" s="3" t="inlineStr"/>
-      <c r="W10" t="n">
-        <v>34</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="3" t="n">
-        <v>-0.1245530606971789</v>
-      </c>
-      <c r="Z10" s="3" t="n">
-        <v>-0.1245530606971789</v>
-      </c>
-      <c r="AA10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>105</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>50</v>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="3" t="n">
-        <v>0.1422736834243421</v>
-      </c>
-      <c r="AF10" s="3" t="n">
-        <v>-0.00450254178599685</v>
-      </c>
-      <c r="AG10" s="3" t="n">
-        <v>0.02957125224090795</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>3</v>
-      </c>
-      <c r="AI10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ10" s="3" t="n">
-        <v>-0.002941135344438864</v>
-      </c>
-      <c r="AK10" s="3" t="n">
-        <v>-2.220446049250313e-16</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AM10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AN10" s="3" t="n">
-        <v>0.10904401508735</v>
-      </c>
-      <c r="AO10" s="3" t="n">
         <v>-0.03077953492302243</v>
       </c>
     </row>

--- a/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_variable_hrp_quarterly.xlsx
+++ b/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_variable_hrp_quarterly.xlsx
@@ -14,7 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C4" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C5" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C6" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="timing" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C7" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="timing" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -917,27 +918,27 @@
         <v>0.798509113087996</v>
       </c>
       <c r="AD3" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AF3" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AH3" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AJ3" s="3" t="inlineStr"/>
@@ -1048,51 +1049,51 @@
         <v>0.6209867237058013</v>
       </c>
       <c r="AD4" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AH4" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AJ4" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AL4" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AN4" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AP4" s="3" t="inlineStr"/>
@@ -1197,51 +1198,51 @@
         <v>0.5810273585142871</v>
       </c>
       <c r="AD5" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AH5" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AJ5" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AL5" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AN5" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AP5" s="3" t="inlineStr"/>
@@ -1346,51 +1347,51 @@
         <v>0.724638030844148</v>
       </c>
       <c r="AD6" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AH6" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AL6" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AN6" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AP6" s="3" t="inlineStr"/>
@@ -1495,51 +1496,51 @@
         <v>0.6669286234028602</v>
       </c>
       <c r="AD7" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AH7" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AJ7" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AL7" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AN7" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AP7" s="3" t="inlineStr"/>
@@ -1644,51 +1645,51 @@
         <v>0.4089398190385178</v>
       </c>
       <c r="AD8" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AH8" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AL8" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AN8" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AP8" s="3" t="inlineStr"/>
@@ -1793,51 +1794,51 @@
         <v>0.6171320252852945</v>
       </c>
       <c r="AD9" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AH9" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AJ9" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AL9" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AN9" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AP9" s="3" t="inlineStr"/>
@@ -2142,66 +2143,68 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>37460</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
+        <v>36038</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>36116</v>
+      </c>
       <c r="M2" t="n">
-        <v>1896</v>
+        <v>86</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>-0.4859401977791229</v>
+        <v>-0.1697286534192363</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>-0.4862309442441406</v>
+        <v>-0.1697286534192363</v>
       </c>
       <c r="P2" t="n">
-        <v>1895</v>
+        <v>85</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>0.265757517207872</v>
+        <v>0.09032004823014436</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>0.265757517207872</v>
+        <v>0.04076898034342898</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
       </c>
       <c r="U2" t="b">
-        <v>1</v>
-      </c>
-      <c r="V2" s="3" t="n">
-        <v>-0.03939252582908825</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="X2" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.4859401977791229</v>
+        <v>-0.1697286534192363</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.4862309442441406</v>
+        <v>-0.1697286534192363</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1313</v>
-      </c>
-      <c r="AC2" t="inlineStr"/>
+        <v>55</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
       <c r="AD2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.9452989626493455</v>
+        <v>0.2044255219913531</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -2249,34 +2252,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>37460</v>
+        <v>36038</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>38012</v>
+        <v>36104</v>
       </c>
       <c r="M3" t="n">
-        <v>963</v>
+        <v>78</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>-0.2928258101948606</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>-0.3309499985899496</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="P3" t="n">
-        <v>813</v>
+        <v>77</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>0.1378626392028849</v>
+        <v>0.08652899115469197</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>0.0982768979428859</v>
+        <v>0.03721870417281659</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -2286,29 +2289,31 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="X3" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.2928258101948606</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.3309499985899496</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>380</v>
-      </c>
-      <c r="AC3" t="inlineStr"/>
+        <v>47</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>-8</v>
+      </c>
       <c r="AD3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.4140787579868381</v>
+        <v>0.1932346188529419</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -2372,78 +2377,76 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>36650</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>36691</v>
-      </c>
+        <v>36038</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>57</v>
+        <v>426</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.05180660636782208</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.07968906534569831</v>
+        <v>-0.1794567831135302</v>
       </c>
       <c r="P4" t="n">
-        <v>45</v>
+        <v>426</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.04755212641183654</v>
+        <v>0.1048961667856762</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.008314770635087161</v>
+        <v>0.1048961667856762</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
       </c>
       <c r="U4" t="b">
-        <v>0</v>
-      </c>
-      <c r="V4" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V4" s="3" t="n">
+        <v>-0.07287826529778774</v>
+      </c>
       <c r="W4" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="X4" t="n">
-        <v>-609</v>
+        <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.05180660636782208</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.07968906534569831</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>28</v>
+        <v>395</v>
       </c>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="b">
         <v>1</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.05463717287606285</v>
+        <v>0.1932346188529419</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.08996212730779873</v>
+        <v>0.06767746261285963</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.2410192038270386</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>-352</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ4" s="3" t="inlineStr"/>
       <c r="AK4" s="3" t="inlineStr"/>
@@ -2495,34 +2498,34 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>37460</v>
+        <v>36038</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>37984</v>
+        <v>36104</v>
       </c>
       <c r="M5" t="n">
-        <v>945</v>
+        <v>78</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-0.2761519972064159</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-0.3151750809469517</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="P5" t="n">
-        <v>772</v>
+        <v>77</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.1234246124375544</v>
+        <v>0.08559690479581393</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0.08715928821578969</v>
+        <v>0.03681778598352924</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -2532,38 +2535,40 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="X5" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.2761519972064159</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.3151750809469517</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>362</v>
-      </c>
-      <c r="AC5" t="inlineStr"/>
+        <v>47</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-8</v>
+      </c>
       <c r="AD5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.3815055041122559</v>
+        <v>0.1932346188529419</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.0111176097270962</v>
+        <v>-0.0004009181892873429</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.01667381298844473</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-18</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -2618,34 +2623,34 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>37460</v>
+        <v>36038</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>39064</v>
+        <v>36262</v>
       </c>
       <c r="M6" t="n">
-        <v>1691</v>
+        <v>184</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.387127877918954</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.4201681847926452</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="P6" t="n">
-        <v>1554</v>
+        <v>183</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.2201700101841288</v>
+        <v>0.102821361010638</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.2079336017943235</v>
+        <v>0.06767920909576697</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -2655,38 +2660,40 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="X6" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.387127877918954</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.4201681847926452</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1108</v>
-      </c>
-      <c r="AC6" t="inlineStr"/>
+        <v>153</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>98</v>
+      </c>
       <c r="AD6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.631661751238475</v>
+        <v>0.1932346188529419</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>0.1096567038514376</v>
+        <v>0.03046050492295038</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>-0.09430206772409333</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>728</v>
+        <v>106</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
@@ -2741,34 +2748,34 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>37460</v>
+        <v>36038</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>38007</v>
+        <v>36104</v>
       </c>
       <c r="M7" t="n">
-        <v>960</v>
+        <v>78</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>-0.3090916103536964</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>-0.3463388996218203</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="P7" t="n">
-        <v>823</v>
+        <v>77</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.1424323535440002</v>
+        <v>0.08559690479581393</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.1013763566202188</v>
+        <v>0.03681778598352924</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
@@ -2778,38 +2785,40 @@
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="X7" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.3090916103536964</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.3463388996218203</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>377</v>
-      </c>
-      <c r="AC7" t="inlineStr"/>
+        <v>47</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-8</v>
+      </c>
       <c r="AD7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.4473698901122469</v>
+        <v>0.1932346188529419</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>0.003099458677332953</v>
+        <v>-0.0004009181892873429</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>-0.01626580015883572</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -2864,75 +2873,73 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>36608</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>37838</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>38303</v>
-      </c>
+        <v>35993</v>
+      </c>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>1166</v>
+        <v>90</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.1457017075496173</v>
+        <v>0</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.2055959130438868</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>791</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.1216014399220798</v>
+        <v>0</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.09537630211584516</v>
+        <v>0</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U8" t="b">
         <v>0</v>
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>844</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>206</v>
+        <v>-31</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.1457017075496173</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.2055959130438868</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>322</v>
-      </c>
-      <c r="AC8" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-55</v>
+      </c>
       <c r="AD8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.1705513271385588</v>
+        <v>0</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>-0.002900595827040733</v>
+        <v>-0.03721870417281659</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.1471241026452433</v>
+        <v>0.1619418476466084</v>
       </c>
       <c r="AH8" t="n">
-        <v>-58</v>
+        <v>-47</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
@@ -2941,8 +2948,12 @@
       <c r="AK8" s="3" t="inlineStr"/>
       <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="inlineStr"/>
-      <c r="AN8" s="3" t="inlineStr"/>
-      <c r="AO8" s="3" t="inlineStr"/>
+      <c r="AN8" s="3" t="n">
+        <v>0.0400589872135646</v>
+      </c>
+      <c r="AO8" s="3" t="n">
+        <v>-0.0366163262770185</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2987,34 +2998,34 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>37460</v>
+        <v>36038</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>37986</v>
+        <v>36104</v>
       </c>
       <c r="M9" t="n">
-        <v>947</v>
+        <v>78</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>-0.2828037839281438</v>
+        <v>-0.158845408661771</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.3401599263032039</v>
+        <v>-0.158845408661771</v>
       </c>
       <c r="P9" t="n">
-        <v>660</v>
+        <v>77</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.1418778148333315</v>
+        <v>0.0853744372621081</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.1002963190039776</v>
+        <v>0.0367220960510042</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T9" t="b">
         <v>0</v>
@@ -3024,38 +3035,40 @@
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="X9" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.2828037839281438</v>
+        <v>-0.158845408661771</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.3401599263032039</v>
+        <v>-0.158845408661771</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>364</v>
-      </c>
-      <c r="AC9" t="inlineStr"/>
+        <v>47</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-8</v>
+      </c>
       <c r="AD9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.3943185666498406</v>
+        <v>0.1888421109478307</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>0.00201942106109175</v>
+        <v>-0.0004966081218123891</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.01002202626671689</v>
+        <v>0.003096438984837357</v>
       </c>
       <c r="AH9" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -3064,8 +3077,12 @@
       <c r="AK9" s="3" t="inlineStr"/>
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr"/>
-      <c r="AN9" s="3" t="inlineStr"/>
-      <c r="AO9" s="3" t="inlineStr"/>
+      <c r="AN9" s="3" t="n">
+        <v>0.0400589872135646</v>
+      </c>
+      <c r="AO9" s="3" t="n">
+        <v>-0.008070410952093265</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3362,68 +3379,66 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" t="n">
+        <v>1895</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.4862309442441406</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.4862309442441406</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1895</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.2658275917027504</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.2658275917027504</v>
+      </c>
+      <c r="S2" s="2" t="n">
         <v>39364</v>
       </c>
-      <c r="K2" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>41124</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1215</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>-0.5035092528573126</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>-0.5040024023286764</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1213</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>0.2354171526922728</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>0.1562892258388244</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>43364</v>
-      </c>
       <c r="T2" t="b">
         <v>0</v>
       </c>
       <c r="U2" t="b">
-        <v>0</v>
-      </c>
-      <c r="V2" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V2" s="3" t="n">
+        <v>-0.03993583465459472</v>
+      </c>
       <c r="W2" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.5035092528573126</v>
+        <v>-0.4862309442441406</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.5040024023286764</v>
+        <v>-0.4862309442441406</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>860</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
+        <v>1313</v>
+      </c>
+      <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>1.014136226616542</v>
+        <v>0.94639982458421</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -3471,34 +3486,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>38007</v>
+      </c>
+      <c r="M3" t="n">
+        <v>959</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.291230325563591</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.3309499985899496</v>
+      </c>
+      <c r="P3" t="n">
+        <v>796</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.1381187240689723</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.09828087349740594</v>
+      </c>
+      <c r="S3" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>40746</v>
-      </c>
-      <c r="M3" t="n">
-        <v>954</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>-0.4439839127181154</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>-0.4439839127181154</v>
-      </c>
-      <c r="P3" t="n">
-        <v>953</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>0.1982156637126214</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>0.1166175213781546</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -3508,31 +3523,29 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.4439839127181154</v>
+        <v>-0.291230325563591</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.4439839127181154</v>
+        <v>-0.3309499985899496</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>599</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>-261</v>
-      </c>
+        <v>377</v>
+      </c>
+      <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.798509113087996</v>
+        <v>0.410895578729674</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -3596,34 +3609,34 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>36650</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>36691</v>
+      </c>
+      <c r="M4" t="n">
+        <v>56</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>-0.04966734844690113</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>-0.07968906534569831</v>
+      </c>
+      <c r="P4" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.04795368197618332</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0.008314578158079504</v>
+      </c>
+      <c r="S4" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>41061</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>41124</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1215</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>-0.09466293283795224</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>-0.1506103472912015</v>
-      </c>
-      <c r="P4" t="n">
-        <v>247</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>0.04847007156721702</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>0.03217841127955078</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -3633,40 +3646,38 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>1171</v>
+        <v>28</v>
       </c>
       <c r="X4" t="n">
-        <v>816</v>
+        <v>-609</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.09466293283795224</v>
+        <v>-0.04966734844690113</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.1506103472912015</v>
+        <v>-0.07968906534569831</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>44</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>-816</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.104560982060186</v>
+        <v>0.05226311898863134</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.08443911009860386</v>
+        <v>-0.08996629533932643</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.3493209798801632</v>
+        <v>0.2415629771166898</v>
       </c>
       <c r="AH4" t="n">
-        <v>-555</v>
+        <v>-349</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -3675,12 +3686,8 @@
       <c r="AK4" s="3" t="inlineStr"/>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
-      <c r="AN4" s="3" t="n">
-        <v>0.1241816912769598</v>
-      </c>
-      <c r="AO4" s="3" t="n">
-        <v>-0.08939590726649083</v>
-      </c>
+      <c r="AN4" s="3" t="inlineStr"/>
+      <c r="AO4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3725,34 +3732,34 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>37984</v>
+      </c>
+      <c r="M5" t="n">
+        <v>944</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>-0.2745188941032745</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>-0.3151750809469518</v>
+      </c>
+      <c r="P5" t="n">
+        <v>756</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0.1234895769810911</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0.08718204274908775</v>
+      </c>
+      <c r="S5" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>40486</v>
-      </c>
-      <c r="M5" t="n">
-        <v>775</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>-0.3674998761946072</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>-0.3674998761946072</v>
-      </c>
-      <c r="P5" t="n">
-        <v>774</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>0.1532547245176266</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>0.08127722777506252</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -3762,40 +3769,38 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.3674998761946072</v>
+        <v>-0.2745188941032745</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.3674998761946072</v>
+        <v>-0.3151750809469518</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>420</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>-440</v>
-      </c>
+        <v>362</v>
+      </c>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.5810273585142876</v>
+        <v>0.3783956492760172</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.03534029360309213</v>
+        <v>-0.01109883074831819</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.07648403652350821</v>
+        <v>0.01671143146031651</v>
       </c>
       <c r="AH5" t="n">
-        <v>-179</v>
+        <v>-15</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -3804,12 +3809,8 @@
       <c r="AK5" s="3" t="inlineStr"/>
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
-      <c r="AN5" s="3" t="n">
-        <v>0.1241816912769598</v>
-      </c>
-      <c r="AO5" s="3" t="n">
-        <v>0.01312838014984941</v>
-      </c>
+      <c r="AN5" s="3" t="inlineStr"/>
+      <c r="AO5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3854,34 +3855,34 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>39056</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1684</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-0.3857451520420616</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-0.4201681847926452</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1538</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.2206013647171226</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.2079643920904948</v>
+      </c>
+      <c r="S6" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>40133</v>
-      </c>
-      <c r="M6" t="n">
-        <v>531</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>-0.2697487878045376</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>-0.2697487878045376</v>
-      </c>
-      <c r="P6" t="n">
-        <v>530</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0.0917109960363139</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0.04027183103505601</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -3891,40 +3892,38 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.2697487878045376</v>
+        <v>-0.3857451520420616</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.2697487878045376</v>
+        <v>-0.4201681847926452</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>176</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>-684</v>
-      </c>
+        <v>1102</v>
+      </c>
+      <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.3693917699822118</v>
+        <v>0.627988779127187</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>-0.07634569034309864</v>
+        <v>0.1096835185930888</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.1742351249135778</v>
+        <v>-0.09451482647847065</v>
       </c>
       <c r="AH6" t="n">
-        <v>-423</v>
+        <v>725</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
@@ -3979,34 +3978,34 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>38007</v>
+      </c>
+      <c r="M7" t="n">
+        <v>959</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>-0.3075328236598556</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>-0.3463388996218203</v>
+      </c>
+      <c r="P7" t="n">
+        <v>813</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0.142506242896548</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0.1014028917883158</v>
+      </c>
+      <c r="S7" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>40567</v>
-      </c>
-      <c r="M7" t="n">
-        <v>829</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>-0.4000942896051511</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>-0.4000942896051511</v>
-      </c>
-      <c r="P7" t="n">
-        <v>828</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>0.1700991045634237</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>0.09329647245376695</v>
-      </c>
-      <c r="S7" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
@@ -4016,40 +4015,38 @@
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.4000942896051511</v>
+        <v>-0.3075328236598556</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.4000942896051511</v>
+        <v>-0.3463388996218203</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>474</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>-386</v>
-      </c>
+        <v>377</v>
+      </c>
+      <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.6669286234028597</v>
+        <v>0.4441117704455546</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>-0.0233210489243877</v>
+        <v>0.003122018290909814</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.04388962311296429</v>
+        <v>-0.01630249809626461</v>
       </c>
       <c r="AH7" t="n">
-        <v>-125</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -4104,34 +4101,34 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>37838</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>38303</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1165</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>-0.1437742902092021</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>-0.2055959130438868</v>
+      </c>
+      <c r="P8" t="n">
+        <v>784</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0.121653308359447</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0.09540124289590783</v>
+      </c>
+      <c r="S8" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>39412</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>40101</v>
-      </c>
-      <c r="M8" t="n">
-        <v>509</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>-0.08264378139658068</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>-0.08264378139658068</v>
-      </c>
-      <c r="P8" t="n">
-        <v>508</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <v>0.04931580087778874</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>0.02120290308064275</v>
-      </c>
-      <c r="S8" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
@@ -4141,40 +4138,38 @@
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>33</v>
+        <v>843</v>
       </c>
       <c r="X8" t="n">
-        <v>-322</v>
+        <v>206</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.08264378139658068</v>
+        <v>-0.1437742902092021</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.08264378139658068</v>
+        <v>-0.2055959130438868</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>476</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>-384</v>
-      </c>
+        <v>322</v>
+      </c>
+      <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.09008908395737203</v>
+        <v>0.1679163432786088</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>-0.0954146182975119</v>
+        <v>-0.002879630601498109</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.3613401313215348</v>
+        <v>0.1474560353543889</v>
       </c>
       <c r="AH8" t="n">
-        <v>-123</v>
+        <v>-55</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
@@ -4229,34 +4224,34 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>37986</v>
+      </c>
+      <c r="M9" t="n">
+        <v>946</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>-0.2811856881932547</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>-0.340159926303204</v>
+      </c>
+      <c r="P9" t="n">
+        <v>639</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>0.1419524244410293</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>0.1003225672834833</v>
+      </c>
+      <c r="S9" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>40546</v>
-      </c>
-      <c r="M9" t="n">
-        <v>815</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>-0.3816212997058295</v>
-      </c>
-      <c r="O9" s="3" t="n">
-        <v>-0.3816212997058295</v>
-      </c>
-      <c r="P9" t="n">
-        <v>814</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>0.1642351393340294</v>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>0.08931724369670038</v>
-      </c>
-      <c r="S9" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T9" t="b">
         <v>0</v>
@@ -4266,40 +4261,38 @@
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.3816212997058295</v>
+        <v>-0.2811856881932547</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.3816212997058295</v>
+        <v>-0.340159926303204</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>460</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>-400</v>
-      </c>
+        <v>364</v>
+      </c>
+      <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.6171320252852943</v>
+        <v>0.3911798688127013</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.02730027768145427</v>
+        <v>0.002041693786077367</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.06236261301228596</v>
+        <v>0.01004463737033623</v>
       </c>
       <c r="AH9" t="n">
-        <v>-139</v>
+        <v>-13</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -4606,34 +4599,34 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>43570</v>
+        <v>41124</v>
       </c>
       <c r="M2" t="n">
-        <v>140</v>
+        <v>1215</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>-0.1954368693665691</v>
+        <v>-0.5035092528573126</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>-0.2022979914860074</v>
+        <v>-0.5040024023286764</v>
       </c>
       <c r="P2" t="n">
-        <v>132</v>
+        <v>1213</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>0.08269444253856398</v>
+        <v>0.2354171526922728</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>0.05218963375687868</v>
+        <v>0.1563175570682493</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
@@ -4643,22 +4636,22 @@
       </c>
       <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.1954368693665691</v>
+        <v>-0.5035092528573126</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.2022979914860074</v>
+        <v>-0.5040024023286764</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>76</v>
+        <v>860</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -4667,7 +4660,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.2429105460160748</v>
+        <v>1.014136226616542</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -4715,34 +4708,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>43542</v>
+        <v>40746</v>
       </c>
       <c r="M3" t="n">
-        <v>120</v>
+        <v>954</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>-0.1379446474939671</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>-0.1410541034597297</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="P3" t="n">
-        <v>116</v>
+        <v>953</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>0.04694464568316091</v>
+        <v>0.1982156637126214</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>0.02744587744229462</v>
+        <v>0.1166386611447342</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -4752,31 +4745,31 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.1379446474939671</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.1410541034597297</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>56</v>
+        <v>599</v>
       </c>
       <c r="AC3" t="n">
-        <v>-20</v>
+        <v>-261</v>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.1600183179571426</v>
+        <v>0.798509113087996</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -4840,34 +4833,34 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>43458</v>
+        <v>41061</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>43537</v>
+        <v>41124</v>
       </c>
       <c r="M4" t="n">
-        <v>117</v>
+        <v>1215</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.133289881480832</v>
+        <v>-0.09466293283795224</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.1410541034597298</v>
+        <v>-0.1506103472912015</v>
       </c>
       <c r="P4" t="n">
-        <v>104</v>
+        <v>247</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.04716738793712075</v>
+        <v>0.04847007156721702</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.02723210412246817</v>
+        <v>0.03218424440046873</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -4877,40 +4870,40 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>64</v>
+        <v>1171</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>816</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.133289881480832</v>
+        <v>-0.09466293283795224</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.1410541034597298</v>
+        <v>-0.1506103472912015</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="AC4" t="n">
-        <v>-23</v>
+        <v>-816</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.1537883066469405</v>
+        <v>0.104560982060186</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.0002137733198264505</v>
+        <v>-0.08445441674426547</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.004654766013135081</v>
+        <v>0.3493209798801632</v>
       </c>
       <c r="AH4" t="n">
-        <v>-3</v>
+        <v>-555</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -4920,10 +4913,10 @@
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
       <c r="AN4" s="3" t="n">
-        <v>0.1656098075061709</v>
+        <v>0.1241816912769598</v>
       </c>
       <c r="AO4" s="3" t="n">
-        <v>-0.1340945703114591</v>
+        <v>-0.08939590726649083</v>
       </c>
     </row>
     <row r="5">
@@ -4969,34 +4962,34 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>43542</v>
+        <v>40486</v>
       </c>
       <c r="M5" t="n">
-        <v>120</v>
+        <v>775</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-0.1391937251083381</v>
+        <v>-0.3674998761946072</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-0.1410541034597297</v>
+        <v>-0.3674998761946072</v>
       </c>
       <c r="P5" t="n">
-        <v>116</v>
+        <v>774</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.04715558064723339</v>
+        <v>0.1532547245176266</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0.02756919917766997</v>
+        <v>0.0812919612525288</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -5006,40 +4999,40 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.1391937251083381</v>
+        <v>-0.3674998761946072</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.1410541034597297</v>
+        <v>-0.3674998761946072</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>56</v>
+        <v>420</v>
       </c>
       <c r="AC5" t="n">
-        <v>-20</v>
+        <v>-440</v>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.1617015688295911</v>
+        <v>0.5810273585142876</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>0.0001233217353753466</v>
+        <v>-0.0353466998922054</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>-0.001249077614370986</v>
+        <v>0.07648403652350821</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>-179</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -5049,10 +5042,10 @@
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
       <c r="AN5" s="3" t="n">
-        <v>0.1656098075061709</v>
+        <v>0.1241816912769598</v>
       </c>
       <c r="AO5" s="3" t="n">
-        <v>0.009509211625454705</v>
+        <v>0.01312838014984941</v>
       </c>
     </row>
     <row r="6">
@@ -5098,34 +5091,34 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>43766</v>
+        <v>40133</v>
       </c>
       <c r="M6" t="n">
-        <v>276</v>
+        <v>531</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.1379446474939671</v>
+        <v>-0.2697487878045376</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.1410541034597297</v>
+        <v>-0.2697487878045376</v>
       </c>
       <c r="P6" t="n">
-        <v>272</v>
+        <v>530</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.05865945403888815</v>
+        <v>0.0917109960363139</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.05188911577288446</v>
+        <v>0.04027913128546222</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -5135,40 +5128,40 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.1379446474939671</v>
+        <v>-0.2697487878045376</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.1410541034597297</v>
+        <v>-0.2697487878045376</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>212</v>
+        <v>176</v>
       </c>
       <c r="AC6" t="n">
-        <v>136</v>
+        <v>-684</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.1600183179571426</v>
+        <v>0.3693917699822118</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>0.02444323833058984</v>
+        <v>-0.07635952985927198</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0</v>
+        <v>0.1742351249135778</v>
       </c>
       <c r="AH6" t="n">
-        <v>156</v>
+        <v>-423</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
@@ -5223,34 +5216,34 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>43559</v>
+        <v>40567</v>
       </c>
       <c r="M7" t="n">
-        <v>133</v>
+        <v>829</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>-0.1379446474939671</v>
+        <v>-0.4000942896051511</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>-0.1410541034597297</v>
+        <v>-0.4000942896051511</v>
       </c>
       <c r="P7" t="n">
-        <v>129</v>
+        <v>828</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.04619261644745546</v>
+        <v>0.1700991045634237</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.02841995137059498</v>
+        <v>0.0933133847121228</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
@@ -5260,40 +5253,40 @@
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.1379446474939671</v>
+        <v>-0.4000942896051511</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.1410541034597297</v>
+        <v>-0.4000942896051511</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>69</v>
+        <v>474</v>
       </c>
       <c r="AC7" t="n">
-        <v>-7</v>
+        <v>-386</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.1600183179571426</v>
+        <v>0.6669286234028597</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>0.0009740739283003591</v>
+        <v>-0.0233252764326114</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0</v>
+        <v>0.04388962311296429</v>
       </c>
       <c r="AH7" t="n">
-        <v>13</v>
+        <v>-125</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -5348,34 +5341,34 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>43458</v>
+        <v>39412</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>43766</v>
+        <v>40101</v>
       </c>
       <c r="M8" t="n">
-        <v>276</v>
+        <v>509</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.1379446474939672</v>
+        <v>-0.08264378139658068</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.1410541034597296</v>
+        <v>-0.08264378139658068</v>
       </c>
       <c r="P8" t="n">
-        <v>272</v>
+        <v>508</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.0586594540388882</v>
+        <v>0.04931580087778874</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.05188911577288451</v>
+        <v>0.02120674662333373</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
@@ -5385,40 +5378,40 @@
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-322</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.1379446474939672</v>
+        <v>-0.08264378139658068</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.1410541034597296</v>
+        <v>-0.08264378139658068</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>212</v>
+        <v>476</v>
       </c>
       <c r="AC8" t="n">
-        <v>136</v>
+        <v>-384</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.1600183179571428</v>
+        <v>0.09008908395737203</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>0.02444323833058989</v>
+        <v>-0.09543191452140047</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>-1.110223024625157e-16</v>
+        <v>0.3613401313215348</v>
       </c>
       <c r="AH8" t="n">
-        <v>156</v>
+        <v>-123</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
@@ -5473,34 +5466,34 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>43559</v>
+        <v>40546</v>
       </c>
       <c r="M9" t="n">
-        <v>133</v>
+        <v>815</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>-0.1379446474939671</v>
+        <v>-0.3816212997058295</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.1410541034597297</v>
+        <v>-0.3816212997058295</v>
       </c>
       <c r="P9" t="n">
-        <v>129</v>
+        <v>814</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.04619261644745546</v>
+        <v>0.1642351393340294</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.02841995137059498</v>
+        <v>0.08933343462290909</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T9" t="b">
         <v>0</v>
@@ -5510,40 +5503,40 @@
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.1379446474939671</v>
+        <v>-0.3816212997058295</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.1410541034597297</v>
+        <v>-0.3816212997058295</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>69</v>
+        <v>460</v>
       </c>
       <c r="AC9" t="n">
-        <v>-7</v>
+        <v>-400</v>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.1600183179571426</v>
+        <v>0.6171320252852943</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>0.0009740739283003591</v>
+        <v>-0.02730522652182511</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0</v>
+        <v>0.06236261301228596</v>
       </c>
       <c r="AH9" t="n">
-        <v>13</v>
+        <v>-139</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -5850,34 +5843,34 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>43572</v>
+      </c>
+      <c r="M2" t="n">
+        <v>143</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.1989728318606708</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.2022979914860072</v>
+      </c>
+      <c r="P2" t="n">
+        <v>138</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.08183226369428324</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.05211846719049073</v>
+      </c>
+      <c r="S2" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>43992</v>
-      </c>
-      <c r="M2" t="n">
-        <v>78</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>-0.2902196151348784</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>-0.2902196151348784</v>
-      </c>
-      <c r="P2" t="n">
-        <v>77</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>0.1403286526425155</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>0.05728893254440421</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
@@ -5887,22 +5880,22 @@
       </c>
       <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.2902196151348784</v>
+        <v>-0.1989728318606708</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.2902196151348784</v>
+        <v>-0.2022979914860072</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -5911,7 +5904,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.4088864968986545</v>
+        <v>0.2483971078320053</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -5959,34 +5952,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>43539</v>
+      </c>
+      <c r="M3" t="n">
+        <v>120</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.1373591481699221</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.1410541034597296</v>
+      </c>
+      <c r="P3" t="n">
+        <v>115</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.04694462358448135</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.0274071811141844</v>
+      </c>
+      <c r="S3" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>44055</v>
-      </c>
-      <c r="M3" t="n">
-        <v>122</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>-0.2902464771828119</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>-0.2902464771828119</v>
-      </c>
-      <c r="P3" t="n">
-        <v>121</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>0.1167974844615735</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>0.05949724743333182</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -5996,31 +5989,31 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1373591481699221</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1410541034597296</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>99</v>
+        <v>55</v>
       </c>
       <c r="AC3" t="n">
-        <v>44</v>
+        <v>-23</v>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.4089398190385185</v>
+        <v>0.1592309799362237</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -6084,83 +6077,91 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>43537</v>
+      </c>
+      <c r="M4" t="n">
+        <v>118</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>-0.1332160003250361</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>-0.1410541034597298</v>
+      </c>
+      <c r="P4" t="n">
+        <v>104</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.04696878752688011</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0.02719372199751205</v>
+      </c>
+      <c r="S4" s="2" t="n">
         <v>43880</v>
       </c>
-      <c r="K4" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" t="n">
-        <v>473</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>-0.290246477182812</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>-0.290246477182812</v>
-      </c>
-      <c r="P4" t="n">
-        <v>473</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>0.2207358717089996</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>0.2207358717089996</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>44564</v>
-      </c>
       <c r="T4" t="b">
         <v>0</v>
       </c>
       <c r="U4" t="b">
-        <v>1</v>
-      </c>
-      <c r="V4" s="3" t="n">
-        <v>-0.2234811907476071</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.290246477182812</v>
+        <v>-0.1332160003250361</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.290246477182812</v>
+        <v>-0.1410541034597298</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>450</v>
-      </c>
-      <c r="AC4" t="inlineStr"/>
+        <v>53</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-25</v>
+      </c>
       <c r="AD4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.4089398190385187</v>
+        <v>0.1536899624070021</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>0.1612386242756678</v>
+        <v>-0.0002134591166723515</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>-1.110223024625157e-16</v>
-      </c>
-      <c r="AH4" t="inlineStr"/>
+        <v>0.004143147844886008</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>-2</v>
+      </c>
       <c r="AI4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ4" s="3" t="inlineStr"/>
       <c r="AK4" s="3" t="inlineStr"/>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
-      <c r="AN4" s="3" t="inlineStr"/>
-      <c r="AO4" s="3" t="inlineStr"/>
+      <c r="AN4" s="3" t="n">
+        <v>0.1648186743793927</v>
+      </c>
+      <c r="AO4" s="3" t="n">
+        <v>-0.1335803124522462</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6205,34 +6206,34 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>43539</v>
+      </c>
+      <c r="M5" t="n">
+        <v>120</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>-0.1372259833597972</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>-0.1410541034597296</v>
+      </c>
+      <c r="P5" t="n">
+        <v>115</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0.04715555864740505</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0.02753032909219467</v>
+      </c>
+      <c r="S5" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>44069</v>
-      </c>
-      <c r="M5" t="n">
-        <v>132</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>-0.2902464771828119</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>-0.2902464771828119</v>
-      </c>
-      <c r="P5" t="n">
-        <v>131</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>0.1201318255357319</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>0.06363480628085999</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -6242,40 +6243,40 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1372259833597972</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1410541034597296</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>109</v>
+        <v>55</v>
       </c>
       <c r="AC5" t="n">
-        <v>54</v>
+        <v>-23</v>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.4089398190385185</v>
+        <v>0.1590520584917241</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>0.004137558847528165</v>
+        <v>0.0001231479780102636</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0</v>
+        <v>0.0001331648101249305</v>
       </c>
       <c r="AH5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -6284,8 +6285,12 @@
       <c r="AK5" s="3" t="inlineStr"/>
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
-      <c r="AN5" s="3" t="inlineStr"/>
-      <c r="AO5" s="3" t="inlineStr"/>
+      <c r="AN5" s="3" t="n">
+        <v>0.1648186743793927</v>
+      </c>
+      <c r="AO5" s="3" t="n">
+        <v>0.0078908934314732</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6330,34 +6335,34 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>43763</v>
+      </c>
+      <c r="M6" t="n">
+        <v>276</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-0.1373591481699221</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-0.1410541034597296</v>
+      </c>
+      <c r="P6" t="n">
+        <v>271</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.05865945403855966</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.05181598097123994</v>
+      </c>
+      <c r="S6" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>44503</v>
-      </c>
-      <c r="M6" t="n">
-        <v>432</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>-0.2902464771828119</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>-0.2902464771828119</v>
-      </c>
-      <c r="P6" t="n">
-        <v>431</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0.1610753648867642</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0.153951491648402</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -6367,40 +6372,40 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1373591481699221</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1410541034597296</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>409</v>
+        <v>211</v>
       </c>
       <c r="AC6" t="n">
-        <v>354</v>
+        <v>133</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.4089398190385185</v>
+        <v>0.1592309799362237</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>0.09445424421507018</v>
+        <v>0.02440879985705554</v>
       </c>
       <c r="AG6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>310</v>
+        <v>156</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
@@ -6455,34 +6460,34 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>43559</v>
+      </c>
+      <c r="M7" t="n">
+        <v>134</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>-0.1373591481699221</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>-0.1410541034597296</v>
+      </c>
+      <c r="P7" t="n">
+        <v>129</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0.04602121468217404</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0.02837989504149722</v>
+      </c>
+      <c r="S7" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>44069</v>
-      </c>
-      <c r="M7" t="n">
-        <v>132</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>-0.2902464771828119</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>-0.2902464771828119</v>
-      </c>
-      <c r="P7" t="n">
-        <v>131</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>0.1201318255357319</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>0.06363480628085999</v>
-      </c>
-      <c r="S7" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
@@ -6492,40 +6497,40 @@
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1373591481699221</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1410541034597296</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>109</v>
+        <v>69</v>
       </c>
       <c r="AC7" t="n">
-        <v>54</v>
+        <v>-9</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.4089398190385185</v>
+        <v>0.1592309799362237</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>0.004137558847528165</v>
+        <v>0.0009727139273128134</v>
       </c>
       <c r="AG7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -6580,76 +6585,80 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>43763</v>
+      </c>
+      <c r="M8" t="n">
+        <v>276</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>-0.1373591481699222</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>-0.1410541034597297</v>
+      </c>
+      <c r="P8" t="n">
+        <v>271</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0.05865945403855988</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0.05181598097124014</v>
+      </c>
+      <c r="S8" s="2" t="n">
         <v>43880</v>
       </c>
-      <c r="K8" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" t="n">
-        <v>473</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>-0.2902464771828118</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>-0.2902464771828118</v>
-      </c>
-      <c r="P8" t="n">
-        <v>473</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <v>0.1998307842766896</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>0.1998307842766896</v>
-      </c>
-      <c r="S8" s="2" t="n">
-        <v>44564</v>
-      </c>
       <c r="T8" t="b">
         <v>0</v>
       </c>
       <c r="U8" t="b">
-        <v>1</v>
-      </c>
-      <c r="V8" s="3" t="n">
-        <v>-0.1772797824616827</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.2902464771828118</v>
+        <v>-0.1373591481699222</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.2902464771828118</v>
+        <v>-0.1410541034597297</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>450</v>
-      </c>
-      <c r="AC8" t="inlineStr"/>
+        <v>211</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>133</v>
+      </c>
       <c r="AD8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.4089398190385183</v>
+        <v>0.1592309799362239</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>0.1403335368433578</v>
+        <v>0.02440879985705574</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>1.110223024625157e-16</v>
-      </c>
-      <c r="AH8" t="inlineStr"/>
+        <v>-1.110223024625157e-16</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>156</v>
+      </c>
       <c r="AI8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ8" s="3" t="inlineStr"/>
       <c r="AK8" s="3" t="inlineStr"/>
@@ -6701,34 +6710,34 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>43559</v>
+      </c>
+      <c r="M9" t="n">
+        <v>134</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>-0.1373591481699221</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>-0.1410541034597296</v>
+      </c>
+      <c r="P9" t="n">
+        <v>129</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>0.04602121468217404</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>0.02837989504149722</v>
+      </c>
+      <c r="S9" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>44069</v>
-      </c>
-      <c r="M9" t="n">
-        <v>132</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>-0.2902464771828119</v>
-      </c>
-      <c r="O9" s="3" t="n">
-        <v>-0.2902464771828119</v>
-      </c>
-      <c r="P9" t="n">
-        <v>131</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>0.1201318255357319</v>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>0.06363480628085999</v>
-      </c>
-      <c r="S9" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T9" t="b">
         <v>0</v>
@@ -6738,40 +6747,40 @@
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1373591481699221</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1410541034597296</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>109</v>
+        <v>69</v>
       </c>
       <c r="AC9" t="n">
-        <v>54</v>
+        <v>-9</v>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.4089398190385185</v>
+        <v>0.1592309799362237</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>0.004137558847528165</v>
+        <v>0.0009727139273128134</v>
       </c>
       <c r="AG9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -7078,34 +7087,34 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>43992</v>
+      </c>
+      <c r="M2" t="n">
+        <v>78</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.2902196151348784</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.2902196151348784</v>
+      </c>
+      <c r="P2" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.1403286526425155</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.05728893254440421</v>
+      </c>
+      <c r="S2" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>44931</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>45250</v>
-      </c>
-      <c r="M2" t="n">
-        <v>473</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>-0.3239608533428744</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>-0.3239608533428744</v>
-      </c>
-      <c r="P2" t="n">
-        <v>472</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>0.1873955345996986</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>0.1456175032694572</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
@@ -7115,22 +7124,22 @@
       </c>
       <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>253</v>
+        <v>23</v>
       </c>
       <c r="X2" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.3239608533428744</v>
+        <v>-0.2902196151348784</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.3239608533428744</v>
+        <v>-0.2902196151348784</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>220</v>
+        <v>55</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -7139,7 +7148,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.4792042812088533</v>
+        <v>0.4088864968986545</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -7187,34 +7196,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>44055</v>
+      </c>
+      <c r="M3" t="n">
+        <v>122</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.2902464771828119</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.2902464771828119</v>
+      </c>
+      <c r="P3" t="n">
+        <v>121</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.1167974844615735</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.05949724743333182</v>
+      </c>
+      <c r="S3" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>44846</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>45131</v>
-      </c>
-      <c r="M3" t="n">
-        <v>389</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>-0.2376608476183659</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>-0.2376608476183659</v>
-      </c>
-      <c r="P3" t="n">
-        <v>388</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>0.1306673287628706</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>0.09210103019783453</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -7224,31 +7233,31 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>195</v>
+        <v>23</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.2376608476183659</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.2376608476183659</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>194</v>
+        <v>99</v>
       </c>
       <c r="AC3" t="n">
-        <v>-26</v>
+        <v>44</v>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.3117521209239831</v>
+        <v>0.4089398190385185</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -7312,91 +7321,83 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" t="n">
+        <v>473</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>-0.290246477182812</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>-0.290246477182812</v>
+      </c>
+      <c r="P4" t="n">
+        <v>473</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.2207358717089996</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0.2207358717089996</v>
+      </c>
+      <c r="S4" s="2" t="n">
         <v>44564</v>
       </c>
-      <c r="K4" s="2" t="n">
-        <v>44846</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>45324</v>
-      </c>
-      <c r="M4" t="n">
-        <v>523</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>-0.205546354512773</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>-0.2093348703683601</v>
-      </c>
-      <c r="P4" t="n">
-        <v>460</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>0.1077262400995233</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>0.0880141131584852</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>45707</v>
-      </c>
       <c r="T4" t="b">
         <v>0</v>
       </c>
       <c r="U4" t="b">
-        <v>0</v>
-      </c>
-      <c r="V4" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V4" s="3" t="n">
+        <v>-0.2234811907476071</v>
+      </c>
       <c r="W4" t="n">
-        <v>195</v>
+        <v>23</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.205546354512773</v>
+        <v>-0.290246477182812</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.2093348703683601</v>
+        <v>-0.290246477182812</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>328</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>108</v>
-      </c>
+        <v>450</v>
+      </c>
+      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.2587266805059651</v>
+        <v>0.4089398190385187</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.004086917039349325</v>
+        <v>0.1612386242756678</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.03211449310559289</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>134</v>
-      </c>
+        <v>-1.110223024625157e-16</v>
+      </c>
+      <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ4" s="3" t="inlineStr"/>
       <c r="AK4" s="3" t="inlineStr"/>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
-      <c r="AN4" s="3" t="n">
-        <v>0.678953431147129</v>
-      </c>
-      <c r="AO4" s="3" t="n">
-        <v>-0.4035884689523094</v>
-      </c>
+      <c r="AN4" s="3" t="inlineStr"/>
+      <c r="AO4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7441,34 +7442,34 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>44069</v>
+      </c>
+      <c r="M5" t="n">
+        <v>132</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>-0.2902464771828119</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>-0.2902464771828119</v>
+      </c>
+      <c r="P5" t="n">
+        <v>131</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0.1201318255357319</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0.06363480628085999</v>
+      </c>
+      <c r="S5" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>44846</v>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>45314</v>
-      </c>
-      <c r="M5" t="n">
-        <v>515</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>-0.2378794616385039</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>-0.2378794616385039</v>
-      </c>
-      <c r="P5" t="n">
-        <v>514</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>0.1252414432874815</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>0.1015402167775275</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -7478,40 +7479,40 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>195</v>
+        <v>23</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.2378794616385039</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.2378794616385039</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>320</v>
+        <v>109</v>
       </c>
       <c r="AC5" t="n">
-        <v>100</v>
+        <v>54</v>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.3121283965787454</v>
+        <v>0.4089398190385185</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>0.009439186579693018</v>
+        <v>0.004137558847528165</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>-0.0002186140201380082</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>126</v>
+        <v>10</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -7520,12 +7521,8 @@
       <c r="AK5" s="3" t="inlineStr"/>
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
-      <c r="AN5" s="3" t="n">
-        <v>0.678953431147129</v>
-      </c>
-      <c r="AO5" s="3" t="n">
-        <v>-0.04772872481844626</v>
-      </c>
+      <c r="AN5" s="3" t="inlineStr"/>
+      <c r="AO5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7570,34 +7567,34 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>44503</v>
+      </c>
+      <c r="M6" t="n">
+        <v>432</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-0.2902464771828119</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-0.2902464771828119</v>
+      </c>
+      <c r="P6" t="n">
+        <v>431</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.1610753648867642</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.153951491648402</v>
+      </c>
+      <c r="S6" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>44628</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>45029</v>
-      </c>
-      <c r="M6" t="n">
-        <v>320</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>-0.1215847395419751</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>-0.1215847395419751</v>
-      </c>
-      <c r="P6" t="n">
-        <v>319</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0.04091496331720496</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0.02616374176240441</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -7607,40 +7604,40 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="X6" t="n">
-        <v>-151</v>
+        <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.1215847395419751</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.1215847395419751</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>276</v>
+        <v>409</v>
       </c>
       <c r="AC6" t="n">
-        <v>56</v>
+        <v>354</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.1384137378016159</v>
+        <v>0.4089398190385185</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>-0.06593728843543012</v>
+        <v>0.09445424421507018</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.1160761080763908</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>82</v>
+        <v>310</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
@@ -7695,34 +7692,34 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>44069</v>
+      </c>
+      <c r="M7" t="n">
+        <v>132</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>-0.2902464771828119</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>-0.2902464771828119</v>
+      </c>
+      <c r="P7" t="n">
+        <v>131</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0.1201318255357319</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0.06363480628085999</v>
+      </c>
+      <c r="S7" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>44729</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>45299</v>
-      </c>
-      <c r="M7" t="n">
-        <v>505</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>-0.222104966978485</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>-0.222104966978485</v>
-      </c>
-      <c r="P7" t="n">
-        <v>504</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>0.1197453439464034</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>0.09613888164566577</v>
-      </c>
-      <c r="S7" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
@@ -7732,40 +7729,40 @@
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>115</v>
+        <v>23</v>
       </c>
       <c r="X7" t="n">
-        <v>-80</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.222104966978485</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.222104966978485</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>390</v>
+        <v>109</v>
       </c>
       <c r="AC7" t="n">
-        <v>170</v>
+        <v>54</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.2855204848342849</v>
+        <v>0.4089398190385185</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>0.004037851447831239</v>
+        <v>0.004137558847528165</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.01555588063988089</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>196</v>
+        <v>10</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -7820,87 +7817,83 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>44564</v>
-      </c>
-      <c r="K8" s="2" t="inlineStr"/>
+        <v>43880</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>43913</v>
+      </c>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>513</v>
+        <v>473</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>0</v>
+        <v>-0.2902464771828118</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.07741687217408422</v>
+        <v>-0.2902464771828118</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>473</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.01276474919454059</v>
+        <v>0.1998307842766896</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0</v>
+        <v>0.1998307842766896</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>45707</v>
+        <v>44564</v>
       </c>
       <c r="T8" t="b">
+        <v>0</v>
+      </c>
+      <c r="U8" t="b">
         <v>1</v>
       </c>
-      <c r="U8" t="b">
-        <v>0</v>
-      </c>
-      <c r="V8" s="3" t="inlineStr"/>
+      <c r="V8" s="3" t="n">
+        <v>-0.1772797824616827</v>
+      </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="X8" t="n">
-        <v>-195</v>
+        <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>0</v>
+        <v>-0.2902464771828118</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>0</v>
+        <v>-0.2902464771828118</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>-220</v>
-      </c>
+        <v>450</v>
+      </c>
+      <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0</v>
+        <v>0.4089398190385183</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>-0.09210103019783453</v>
+        <v>0.1403335368433578</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.2376608476183659</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>-194</v>
-      </c>
+        <v>1.110223024625157e-16</v>
+      </c>
+      <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ8" s="3" t="inlineStr"/>
       <c r="AK8" s="3" t="inlineStr"/>
       <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="inlineStr"/>
-      <c r="AN8" s="3" t="n">
-        <v>0.09967003453281076</v>
-      </c>
-      <c r="AO8" s="3" t="n">
-        <v>-0.09051009422763445</v>
-      </c>
+      <c r="AN8" s="3" t="inlineStr"/>
+      <c r="AO8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7945,34 +7938,34 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>44069</v>
+      </c>
+      <c r="M9" t="n">
+        <v>132</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>-0.2902464771828119</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>-0.2902464771828119</v>
+      </c>
+      <c r="P9" t="n">
+        <v>131</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>0.1201318255357319</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>0.06363480628085999</v>
+      </c>
+      <c r="S9" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>44729</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>45310</v>
-      </c>
-      <c r="M9" t="n">
-        <v>513</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>-0.2217386103320992</v>
-      </c>
-      <c r="O9" s="3" t="n">
-        <v>-0.2217386103320992</v>
-      </c>
-      <c r="P9" t="n">
-        <v>512</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>0.120308212821147</v>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>0.09735135630629647</v>
-      </c>
-      <c r="S9" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T9" t="b">
         <v>0</v>
@@ -7982,40 +7975,40 @@
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>115</v>
+        <v>23</v>
       </c>
       <c r="X9" t="n">
-        <v>-80</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.2217386103320992</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.2217386103320992</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>398</v>
+        <v>109</v>
       </c>
       <c r="AC9" t="n">
-        <v>178</v>
+        <v>54</v>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.2849153424233462</v>
+        <v>0.4089398190385185</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>0.005250326108461947</v>
+        <v>0.004137558847528165</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.01592223728626674</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>204</v>
+        <v>10</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -8024,12 +8017,8 @@
       <c r="AK9" s="3" t="inlineStr"/>
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr"/>
-      <c r="AN9" s="3" t="n">
-        <v>0.09967003453281076</v>
-      </c>
-      <c r="AO9" s="3" t="n">
-        <v>-0.001640172913999871</v>
-      </c>
+      <c r="AN9" s="3" t="inlineStr"/>
+      <c r="AO9" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8326,34 +8315,34 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>44931</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>45250</v>
+      </c>
+      <c r="M2" t="n">
+        <v>473</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.3239608533428744</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.3239608533428744</v>
+      </c>
+      <c r="P2" t="n">
+        <v>472</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.1873955345996986</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.1456175032694572</v>
+      </c>
+      <c r="S2" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>45835</v>
-      </c>
-      <c r="M2" t="n">
-        <v>89</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>-0.2242012270138071</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>-0.2242012270138071</v>
-      </c>
-      <c r="P2" t="n">
-        <v>88</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>0.1032426212645815</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>0.06633642004451831</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
@@ -8363,22 +8352,22 @@
       </c>
       <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>34</v>
+        <v>253</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.2242012270138071</v>
+        <v>-0.3239608533428744</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.2242012270138071</v>
+        <v>-0.3239608533428744</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>55</v>
+        <v>220</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -8387,7 +8376,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.2889940469367012</v>
+        <v>0.4792042812088533</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -8435,34 +8424,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>44846</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>45131</v>
+      </c>
+      <c r="M3" t="n">
+        <v>389</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.2376608476183659</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.2376608476183659</v>
+      </c>
+      <c r="P3" t="n">
+        <v>388</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.1306673287628706</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.09210103019783453</v>
+      </c>
+      <c r="S3" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>45904</v>
-      </c>
-      <c r="M3" t="n">
-        <v>136</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>-0.1541243129380868</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>-0.1541243129380868</v>
-      </c>
-      <c r="P3" t="n">
-        <v>135</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>0.06348808787815403</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>0.05032969331821049</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -8472,31 +8461,31 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>34</v>
+        <v>195</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.2376608476183659</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.2376608476183659</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>102</v>
+        <v>194</v>
       </c>
       <c r="AC3" t="n">
-        <v>47</v>
+        <v>-26</v>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.1822068127687015</v>
+        <v>0.3117521209239831</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -8560,73 +8549,77 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>44846</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>45324</v>
+      </c>
+      <c r="M4" t="n">
+        <v>523</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>-0.205546354512773</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>-0.2093348703683601</v>
+      </c>
+      <c r="P4" t="n">
+        <v>460</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.1077262400995233</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0.0880141131584852</v>
+      </c>
+      <c r="S4" s="2" t="n">
         <v>45707</v>
       </c>
-      <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" t="n">
-        <v>88</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>46021</v>
-      </c>
       <c r="T4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U4" t="b">
         <v>0</v>
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>195</v>
       </c>
       <c r="X4" t="n">
-        <v>-34</v>
+        <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>0</v>
+        <v>-0.205546354512773</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>0</v>
+        <v>-0.2093348703683601</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>328</v>
       </c>
       <c r="AC4" t="n">
-        <v>-55</v>
+        <v>108</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0</v>
+        <v>0.2587266805059651</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.05032969331821049</v>
+        <v>-0.004086917039349325</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.1541243129380868</v>
+        <v>0.03211449310559289</v>
       </c>
       <c r="AH4" t="n">
-        <v>-102</v>
+        <v>134</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -8636,10 +8629,10 @@
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
       <c r="AN4" s="3" t="n">
-        <v>0.10904401508735</v>
+        <v>0.678953431147129</v>
       </c>
       <c r="AO4" s="3" t="n">
-        <v>-0.08356097205346547</v>
+        <v>-0.4035884689523094</v>
       </c>
     </row>
     <row r="5">
@@ -8685,34 +8678,34 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>44846</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>45314</v>
+      </c>
+      <c r="M5" t="n">
+        <v>515</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>-0.2378794616385039</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>-0.2378794616385039</v>
+      </c>
+      <c r="P5" t="n">
+        <v>514</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0.1252414432874815</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0.1015402167775275</v>
+      </c>
+      <c r="S5" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>45911</v>
-      </c>
-      <c r="M5" t="n">
-        <v>141</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>-0.1245530606971789</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>-0.1245530606971789</v>
-      </c>
-      <c r="P5" t="n">
-        <v>140</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>0.0604256839259576</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>0.04876828687665268</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -8722,40 +8715,40 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>34</v>
+        <v>195</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.1245530606971789</v>
+        <v>-0.2378794616385039</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.1245530606971789</v>
+        <v>-0.2378794616385039</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>107</v>
+        <v>320</v>
       </c>
       <c r="AC5" t="n">
-        <v>52</v>
+        <v>100</v>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.1422736834243421</v>
+        <v>0.3121283965787454</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.001561406441557806</v>
+        <v>0.009439186579693018</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.02957125224090795</v>
+        <v>-0.0002186140201380082</v>
       </c>
       <c r="AH5" t="n">
-        <v>5</v>
+        <v>126</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -8765,10 +8758,10 @@
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
       <c r="AN5" s="3" t="n">
-        <v>0.10904401508735</v>
+        <v>0.678953431147129</v>
       </c>
       <c r="AO5" s="3" t="n">
-        <v>-0.03077953492302243</v>
+        <v>-0.04772872481844626</v>
       </c>
     </row>
     <row r="6">
@@ -8814,73 +8807,77 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>44628</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>45029</v>
+      </c>
+      <c r="M6" t="n">
+        <v>320</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-0.1215847395419751</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-0.1215847395419751</v>
+      </c>
+      <c r="P6" t="n">
+        <v>319</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.04091496331720496</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.02616374176240441</v>
+      </c>
+      <c r="S6" s="2" t="n">
         <v>45707</v>
       </c>
-      <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" t="n">
-        <v>88</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>-0.004757784175502544</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>46021</v>
-      </c>
       <c r="T6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="X6" t="n">
-        <v>-34</v>
+        <v>-151</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.004757784175502544</v>
+        <v>-0.1215847395419751</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>0</v>
+        <v>-0.1215847395419751</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>276</v>
       </c>
       <c r="AC6" t="n">
-        <v>-55</v>
+        <v>56</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0</v>
+        <v>0.1384137378016159</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>-0.05032969331821049</v>
+        <v>-0.06593728843543012</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.1493665287625843</v>
+        <v>0.1160761080763908</v>
       </c>
       <c r="AH6" t="n">
-        <v>-102</v>
+        <v>82</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
@@ -8889,12 +8886,8 @@
       <c r="AK6" s="3" t="inlineStr"/>
       <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="inlineStr"/>
-      <c r="AN6" s="3" t="n">
-        <v>0.06587707306593193</v>
-      </c>
-      <c r="AO6" s="3" t="n">
-        <v>-0.05707000491572445</v>
-      </c>
+      <c r="AN6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8939,34 +8932,34 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>44729</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>45299</v>
+      </c>
+      <c r="M7" t="n">
+        <v>505</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>-0.222104966978485</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>-0.222104966978485</v>
+      </c>
+      <c r="P7" t="n">
+        <v>504</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0.1197453439464034</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0.09613888164566577</v>
+      </c>
+      <c r="S7" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>45909</v>
-      </c>
-      <c r="M7" t="n">
-        <v>139</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>-0.1245530606971789</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>-0.1245530606971789</v>
-      </c>
-      <c r="P7" t="n">
-        <v>138</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>0.05718565405934494</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>0.04582715153221364</v>
-      </c>
-      <c r="S7" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
@@ -8976,40 +8969,40 @@
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>34</v>
+        <v>115</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-80</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.1245530606971789</v>
+        <v>-0.222104966978485</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.1245530606971789</v>
+        <v>-0.222104966978485</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>105</v>
+        <v>390</v>
       </c>
       <c r="AC7" t="n">
-        <v>50</v>
+        <v>170</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.1422736834243421</v>
+        <v>0.2855204848342849</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>-0.00450254178599685</v>
+        <v>0.004037851447831239</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.02957125224090795</v>
+        <v>0.01555588063988089</v>
       </c>
       <c r="AH7" t="n">
-        <v>3</v>
+        <v>196</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -9018,12 +9011,8 @@
       <c r="AK7" s="3" t="inlineStr"/>
       <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="inlineStr"/>
-      <c r="AN7" s="3" t="n">
-        <v>0.06587707306593193</v>
-      </c>
-      <c r="AO7" s="3" t="n">
-        <v>0.002524249698548031</v>
-      </c>
+      <c r="AN7" s="3" t="inlineStr"/>
+      <c r="AO7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9068,30 +9057,30 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>45707</v>
+        <v>44564</v>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>88</v>
+        <v>513</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.004757784175502544</v>
+        <v>0</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>0</v>
+        <v>-0.07741687217408422</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0</v>
+        <v>0.01276474919454059</v>
       </c>
       <c r="R8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>46021</v>
+        <v>45707</v>
       </c>
       <c r="T8" t="b">
         <v>1</v>
@@ -9104,10 +9093,10 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-34</v>
+        <v>-195</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.004757784175502544</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="3" t="n">
         <v>0</v>
@@ -9119,7 +9108,7 @@
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>-55</v>
+        <v>-220</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
@@ -9128,13 +9117,13 @@
         <v>0</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>-0.05032969331821049</v>
+        <v>-0.09210103019783453</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.1493665287625843</v>
+        <v>0.2376608476183659</v>
       </c>
       <c r="AH8" t="n">
-        <v>-102</v>
+        <v>-194</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
@@ -9144,10 +9133,10 @@
       <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="inlineStr"/>
       <c r="AN8" s="3" t="n">
-        <v>0.10904401508735</v>
+        <v>0.09967003453281076</v>
       </c>
       <c r="AO8" s="3" t="n">
-        <v>-0.08356097205346547</v>
+        <v>-0.09051009422763445</v>
       </c>
     </row>
     <row r="9">
@@ -9193,34 +9182,34 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>44729</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>45310</v>
+      </c>
+      <c r="M9" t="n">
+        <v>513</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>-0.2217386103320992</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>-0.2217386103320992</v>
+      </c>
+      <c r="P9" t="n">
+        <v>512</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>0.120308212821147</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>0.09735135630629647</v>
+      </c>
+      <c r="S9" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>45909</v>
-      </c>
-      <c r="M9" t="n">
-        <v>139</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>-0.1245530606971789</v>
-      </c>
-      <c r="O9" s="3" t="n">
-        <v>-0.1245530606971789</v>
-      </c>
-      <c r="P9" t="n">
-        <v>138</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>0.05718565405934494</v>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>0.04582715153221364</v>
-      </c>
-      <c r="S9" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T9" t="b">
         <v>0</v>
@@ -9230,40 +9219,40 @@
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>34</v>
+        <v>115</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-80</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.1245530606971789</v>
+        <v>-0.2217386103320992</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.1245530606971789</v>
+        <v>-0.2217386103320992</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>105</v>
+        <v>398</v>
       </c>
       <c r="AC9" t="n">
-        <v>50</v>
+        <v>178</v>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.1422736834243421</v>
+        <v>0.2849153424233462</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.00450254178599685</v>
+        <v>0.005250326108461947</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.02957125224090795</v>
+        <v>0.01592223728626674</v>
       </c>
       <c r="AH9" t="n">
-        <v>3</v>
+        <v>204</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -9273,10 +9262,10 @@
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" s="3" t="n">
-        <v>0.10904401508735</v>
+        <v>0.09967003453281076</v>
       </c>
       <c r="AO9" s="3" t="n">
-        <v>-0.03077953492302243</v>
+        <v>-0.001640172913999871</v>
       </c>
     </row>
   </sheetData>
@@ -9290,7 +9279,1255 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:AO9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="19" customWidth="1" min="18" max="18"/>
+    <col width="17" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="20" customWidth="1" min="21" max="21"/>
+    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="21" customWidth="1" min="24" max="24"/>
+    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="24" customWidth="1" min="27" max="27"/>
+    <col width="10" customWidth="1" min="28" max="28"/>
+    <col width="19" customWidth="1" min="29" max="29"/>
+    <col width="23" customWidth="1" min="30" max="30"/>
+    <col width="20" customWidth="1" min="31" max="31"/>
+    <col width="19" customWidth="1" min="32" max="32"/>
+    <col width="18" customWidth="1" min="33" max="33"/>
+    <col width="17" customWidth="1" min="34" max="34"/>
+    <col width="21" customWidth="1" min="35" max="35"/>
+    <col width="17" customWidth="1" min="36" max="36"/>
+    <col width="16" customWidth="1" min="37" max="37"/>
+    <col width="15" customWidth="1" min="38" max="38"/>
+    <col width="19" customWidth="1" min="39" max="39"/>
+    <col width="14" customWidth="1" min="40" max="40"/>
+    <col width="17" customWidth="1" min="41" max="41"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>frequency</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>base_run</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>fallback_run</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>detector</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>series</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>crisis_target</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>peak_date</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>trough_date</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>recovery_date</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>full_days</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>full_anchored_dd</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>full_hwm_dd</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>full_days_underwater</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>full_ulcer</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>full_ulcer_common</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>full_common_end</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>full_no_drawdown</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>full_not_recovered</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>full_gap_at_cutoff</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_days</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_days_vs_defined</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_depth</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_max_dd</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_trough_at_boundary</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_days</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_days_vs_bench</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_vs_bench_censored</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_return_to_even</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>full_d_base_ulcer</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_d_base_depth</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_base_days</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_base_censored</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>full_d_fb_ulcer</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_d_fb_depth</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_fb_days</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_fb_censored</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>missed_rally</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>pre_peak_d_base</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>market_cap</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>mcap_t_10</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>benchmark</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>45835</v>
+      </c>
+      <c r="M2" t="n">
+        <v>89</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.2242012270138071</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.2242012270138071</v>
+      </c>
+      <c r="P2" t="n">
+        <v>88</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.1032426212645815</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.06633642004451831</v>
+      </c>
+      <c r="S2" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" s="3" t="inlineStr"/>
+      <c r="W2" t="n">
+        <v>34</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="3" t="n">
+        <v>-0.2242012270138071</v>
+      </c>
+      <c r="Z2" s="3" t="n">
+        <v>-0.2242012270138071</v>
+      </c>
+      <c r="AA2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="3" t="n">
+        <v>0.2889940469367012</v>
+      </c>
+      <c r="AF2" s="3" t="inlineStr"/>
+      <c r="AG2" s="3" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" s="3" t="inlineStr"/>
+      <c r="AK2" s="3" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" s="3" t="inlineStr"/>
+      <c r="AO2" s="3" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>45904</v>
+      </c>
+      <c r="M3" t="n">
+        <v>136</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="P3" t="n">
+        <v>135</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.06348808787815403</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.05032969331821049</v>
+      </c>
+      <c r="S3" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T3" t="b">
+        <v>0</v>
+      </c>
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" s="3" t="inlineStr"/>
+      <c r="W3" t="n">
+        <v>34</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="3" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="Z3" s="3" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="AA3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>102</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>47</v>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="3" t="n">
+        <v>0.1822068127687015</v>
+      </c>
+      <c r="AF3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="3" t="inlineStr"/>
+      <c r="AK3" s="3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" s="3" t="inlineStr"/>
+      <c r="AO3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" t="n">
+        <v>89</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T4" t="b">
+        <v>1</v>
+      </c>
+      <c r="U4" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" s="3" t="inlineStr"/>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-34</v>
+      </c>
+      <c r="Y4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-55</v>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" s="3" t="n">
+        <v>-0.05032969331821049</v>
+      </c>
+      <c r="AG4" s="3" t="n">
+        <v>0.1541243129380868</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>-102</v>
+      </c>
+      <c r="AI4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" s="3" t="n">
+        <v>0.10904401508735</v>
+      </c>
+      <c r="AO4" s="3" t="n">
+        <v>-0.08356097205346547</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>min_var</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>45911</v>
+      </c>
+      <c r="M5" t="n">
+        <v>141</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>-0.1245530606971789</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>-0.1245530606971789</v>
+      </c>
+      <c r="P5" t="n">
+        <v>140</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0.0604256839259576</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0.04876828687665268</v>
+      </c>
+      <c r="S5" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T5" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" s="3" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>34</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="3" t="n">
+        <v>-0.1245530606971789</v>
+      </c>
+      <c r="Z5" s="3" t="n">
+        <v>-0.1245530606971789</v>
+      </c>
+      <c r="AA5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>107</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>52</v>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="3" t="n">
+        <v>0.1422736834243421</v>
+      </c>
+      <c r="AF5" s="3" t="n">
+        <v>-0.001561406441557806</v>
+      </c>
+      <c r="AG5" s="3" t="n">
+        <v>0.02957125224090795</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" s="3" t="n">
+        <v>0.10904401508735</v>
+      </c>
+      <c r="AO5" s="3" t="n">
+        <v>-0.03077953492302243</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>89</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-0.004757784175502544</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T6" t="b">
+        <v>1</v>
+      </c>
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" s="3" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-34</v>
+      </c>
+      <c r="Y6" s="3" t="n">
+        <v>-0.004757784175502544</v>
+      </c>
+      <c r="Z6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-55</v>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="3" t="n">
+        <v>-0.05032969331821049</v>
+      </c>
+      <c r="AG6" s="3" t="n">
+        <v>0.1493665287625843</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-102</v>
+      </c>
+      <c r="AI6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" s="3" t="n">
+        <v>0.06587707306593193</v>
+      </c>
+      <c r="AO6" s="3" t="n">
+        <v>-0.05707000491572445</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>min_var</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>45909</v>
+      </c>
+      <c r="M7" t="n">
+        <v>139</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>-0.1245530606971789</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>-0.1245530606971789</v>
+      </c>
+      <c r="P7" t="n">
+        <v>138</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0.05718565405934494</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0.04582715153221364</v>
+      </c>
+      <c r="S7" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T7" t="b">
+        <v>0</v>
+      </c>
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" s="3" t="inlineStr"/>
+      <c r="W7" t="n">
+        <v>34</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="3" t="n">
+        <v>-0.1245530606971789</v>
+      </c>
+      <c r="Z7" s="3" t="n">
+        <v>-0.1245530606971789</v>
+      </c>
+      <c r="AA7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>105</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>50</v>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="3" t="n">
+        <v>0.1422736834243421</v>
+      </c>
+      <c r="AF7" s="3" t="n">
+        <v>-0.00450254178599685</v>
+      </c>
+      <c r="AG7" s="3" t="n">
+        <v>0.02957125224090795</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" s="3" t="n">
+        <v>0.06587707306593193</v>
+      </c>
+      <c r="AO7" s="3" t="n">
+        <v>0.002524249698548031</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" t="n">
+        <v>89</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>-0.004757784175502544</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T8" t="b">
+        <v>1</v>
+      </c>
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" s="3" t="inlineStr"/>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-34</v>
+      </c>
+      <c r="Y8" s="3" t="n">
+        <v>-0.004757784175502544</v>
+      </c>
+      <c r="Z8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-55</v>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="3" t="n">
+        <v>-0.05032969331821049</v>
+      </c>
+      <c r="AG8" s="3" t="n">
+        <v>0.1493665287625843</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>-102</v>
+      </c>
+      <c r="AI8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" s="3" t="n">
+        <v>0.10904401508735</v>
+      </c>
+      <c r="AO8" s="3" t="n">
+        <v>-0.08356097205346547</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>min_var</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>45909</v>
+      </c>
+      <c r="M9" t="n">
+        <v>139</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>-0.1245530606971789</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>-0.1245530606971789</v>
+      </c>
+      <c r="P9" t="n">
+        <v>138</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>0.05718565405934494</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>0.04582715153221364</v>
+      </c>
+      <c r="S9" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T9" t="b">
+        <v>0</v>
+      </c>
+      <c r="U9" t="b">
+        <v>0</v>
+      </c>
+      <c r="V9" s="3" t="inlineStr"/>
+      <c r="W9" t="n">
+        <v>34</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="3" t="n">
+        <v>-0.1245530606971789</v>
+      </c>
+      <c r="Z9" s="3" t="n">
+        <v>-0.1245530606971789</v>
+      </c>
+      <c r="AA9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>105</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>50</v>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="3" t="n">
+        <v>0.1422736834243421</v>
+      </c>
+      <c r="AF9" s="3" t="n">
+        <v>-0.00450254178599685</v>
+      </c>
+      <c r="AG9" s="3" t="n">
+        <v>0.02957125224090795</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" s="3" t="n">
+        <v>0.10904401508735</v>
+      </c>
+      <c r="AO9" s="3" t="n">
+        <v>-0.03077953492302243</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -9396,24 +10633,22 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="E2" s="4" t="n">
-        <v>197</v>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>373</v>
-      </c>
+      <c r="E2" s="4" t="inlineStr"/>
+      <c r="F2" s="4" t="inlineStr"/>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>23</v>
+      </c>
       <c r="J2" s="3" t="n">
-        <v>0.4736842105263158</v>
+        <v>0.4111111111111111</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
         <v>2</v>
@@ -9444,20 +10679,20 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-131</v>
+        <v>196</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>523</v>
+        <v>373</v>
       </c>
       <c r="G3" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="3" t="n">
-        <v>0.7281976744186046</v>
+        <v>0.473655019412091</v>
       </c>
       <c r="K3" t="n">
         <v>3</v>
@@ -9491,23 +10726,23 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>-120</v>
+        <v>-131</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-57</v>
+        <v>523</v>
       </c>
       <c r="G4" t="n">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="3" t="n">
-        <v>0.04137931034482759</v>
+        <v>0.7281976744186046</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L4" t="n">
         <v>2</v>
@@ -9537,19 +10772,21 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr"/>
+      <c r="E5" s="4" t="n">
+        <v>-119</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>-57</v>
+      </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="H5" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" t="n">
-        <v>8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" s="3" t="n">
-        <v>0.7540983606557377</v>
+        <v>0.04794520547945205</v>
       </c>
       <c r="K5" t="n">
         <v>1</v>
@@ -9582,24 +10819,22 @@
           <t>C5</t>
         </is>
       </c>
-      <c r="E6" s="4" t="n">
-        <v>-442</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>-132</v>
-      </c>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>442</v>
+        <v>0</v>
       </c>
       <c r="H6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>8</v>
+      </c>
       <c r="J6" s="3" t="n">
-        <v>0.3625730994152047</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>2</v>
@@ -9630,21 +10865,23 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-94</v>
-      </c>
-      <c r="F7" s="4" t="inlineStr"/>
+        <v>-442</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>-132</v>
+      </c>
       <c r="G7" t="n">
-        <v>94</v>
+        <v>442</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" s="3" t="n">
-        <v>1</v>
+        <v>0.3625730994152047</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
         <v>2</v>
@@ -9661,37 +10898,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>changepoint</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>vix</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>259</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>59</v>
-      </c>
+        <v>-94</v>
+      </c>
+      <c r="F8" s="4" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="H8" t="b">
         <v>0</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" s="3" t="n">
-        <v>0.1058171745152355</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>2</v>
@@ -9718,27 +10953,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>59</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>-43</v>
-      </c>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr"/>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="b">
-        <v>0</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>23</v>
+      </c>
       <c r="J9" s="3" t="n">
-        <v>0.3204941860465116</v>
+        <v>0.4111111111111111</v>
       </c>
       <c r="K9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>2</v>
@@ -9765,25 +10998,27 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr"/>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>258</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>59</v>
+      </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="b">
-        <v>1</v>
-      </c>
-      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" s="3" t="n">
+        <v>0.1059345535219079</v>
+      </c>
+      <c r="K10" t="n">
         <v>6</v>
-      </c>
-      <c r="J10" s="3" t="n">
-        <v>0.4206896551724138</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2</v>
       </c>
       <c r="L10" t="n">
         <v>2</v>
@@ -9810,25 +11045,27 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr"/>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>-43</v>
+      </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="b">
-        <v>1</v>
-      </c>
-      <c r="I11" t="n">
-        <v>8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" s="3" t="n">
-        <v>0.7540983606557377</v>
+        <v>0.3204941860465116</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L11" t="n">
         <v>2</v>
@@ -9855,24 +11092,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>C5</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>63</v>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>119</v>
-      </c>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr"/>
+      <c r="F12" s="4" t="inlineStr"/>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="b">
-        <v>0</v>
-      </c>
-      <c r="I12" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>6</v>
+      </c>
       <c r="J12" s="3" t="n">
-        <v>0.4892787524366471</v>
+        <v>0.4178082191780822</v>
       </c>
       <c r="K12" t="n">
         <v>2</v>
@@ -9902,27 +11137,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>C6</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>-30</v>
-      </c>
-      <c r="F13" s="4" t="n">
-        <v>58</v>
-      </c>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H13" t="b">
-        <v>0</v>
-      </c>
-      <c r="I13" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>8</v>
+      </c>
       <c r="J13" s="3" t="n">
+        <v>0.7619047619047619</v>
+      </c>
+      <c r="K13" t="n">
         <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>2</v>
@@ -9939,24 +11172,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>8</v>
+        <v>63</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>183</v>
+        <v>119</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -9966,10 +11199,10 @@
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" s="3" t="n">
-        <v>0.313573407202216</v>
+        <v>0.4892787524366471</v>
       </c>
       <c r="K14" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L14" t="n">
         <v>2</v>
@@ -9986,37 +11219,37 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>59</v>
+        <v>-30</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>145</v>
+        <v>58</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H15" t="b">
         <v>0</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" s="3" t="n">
-        <v>0.4585755813953488</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>2</v>
@@ -10043,25 +11276,27 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr"/>
-      <c r="F16" s="4" t="inlineStr"/>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>339</v>
+      </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H16" t="b">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I16" t="n">
-        <v>6</v>
-      </c>
-      <c r="J16" s="3" t="n">
-        <v>0.4206896551724138</v>
-      </c>
       <c r="K16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>2</v>
@@ -10088,25 +11323,27 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="4" t="inlineStr"/>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>183</v>
+      </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="b">
-        <v>1</v>
-      </c>
-      <c r="I17" t="n">
-        <v>8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" s="3" t="n">
-        <v>0.7540983606557377</v>
+        <v>0.3139212423738214</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L17" t="n">
         <v>2</v>
@@ -10133,27 +11370,27 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-63</v>
+        <v>59</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>181</v>
+        <v>145</v>
       </c>
       <c r="G18" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="H18" t="b">
         <v>0</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" s="3" t="n">
-        <v>0.7309941520467836</v>
+        <v>0.4585755813953488</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L18" t="n">
         <v>2</v>
@@ -10180,32 +11417,169 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>C6</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>-94</v>
-      </c>
-      <c r="F19" s="4" t="n">
-        <v>58</v>
-      </c>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr"/>
       <c r="G19" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="H19" t="b">
-        <v>0</v>
-      </c>
-      <c r="I19" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>6</v>
+      </c>
       <c r="J19" s="3" t="n">
-        <v>1</v>
+        <v>0.4178082191780822</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L19" t="n">
         <v>2</v>
       </c>
       <c r="M19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr"/>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="b">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>8</v>
+      </c>
+      <c r="J20" s="3" t="n">
+        <v>0.7619047619047619</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>-63</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>181</v>
+      </c>
+      <c r="G21" t="n">
+        <v>63</v>
+      </c>
+      <c r="H21" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" s="3" t="n">
+        <v>0.7309941520467836</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2</v>
+      </c>
+      <c r="M21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>-94</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="G22" t="n">
+        <v>94</v>
+      </c>
+      <c r="H22" t="b">
+        <v>0</v>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2</v>
+      </c>
+      <c r="M22" t="b">
         <v>1</v>
       </c>
     </row>
